--- a/AFマスター.xlsx
+++ b/AFマスター.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://api.box.com/wopi/files/1958820397666/WOPIServiceId_TP_BOX_2/WOPIUserId_-/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="108" documentId="8_{46342269-F254-4CAD-B1DA-15D9221C87F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0D52F5AD-B394-4F2D-8588-57512989A887}"/>
+  <xr:revisionPtr revIDLastSave="164" documentId="8_{46342269-F254-4CAD-B1DA-15D9221C87F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{77D7D1D0-360B-4F28-9856-E7F4A36D984B}"/>
   <bookViews>
-    <workbookView xWindow="43095" yWindow="0" windowWidth="14610" windowHeight="15585" xr2:uid="{56E37DC4-DFDA-413A-A4E6-1369CBF9CBF7}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{56E37DC4-DFDA-413A-A4E6-1369CBF9CBF7}"/>
   </bookViews>
   <sheets>
     <sheet name="割り振りマスター" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="932" uniqueCount="451">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="983" uniqueCount="468">
   <si>
     <t>AFコード</t>
   </si>
@@ -1585,12 +1585,6 @@
     <t>KKL011</t>
   </si>
   <si>
-    <t>DGB122R0</t>
-  </si>
-  <si>
-    <t>DGB123R0</t>
-  </si>
-  <si>
     <t>クレジットカード広告（みずほ券面）</t>
     <rPh sb="8" eb="10">
       <t>コウコク</t>
@@ -1629,6 +1623,65 @@
       <t>ケンメン</t>
     </rPh>
     <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>DGB122</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>DGB123</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>LTG031</t>
+  </si>
+  <si>
+    <t>LTG032</t>
+  </si>
+  <si>
+    <t>LTG033</t>
+  </si>
+  <si>
+    <t>LTG051</t>
+  </si>
+  <si>
+    <t>LTG052</t>
+  </si>
+  <si>
+    <t>LTG053</t>
+  </si>
+  <si>
+    <t>LTG054</t>
+  </si>
+  <si>
+    <t>LTG055</t>
+  </si>
+  <si>
+    <t>LTG056</t>
+  </si>
+  <si>
+    <t>LTG057</t>
+  </si>
+  <si>
+    <t>LTG058</t>
+  </si>
+  <si>
+    <t>LTG059</t>
+  </si>
+  <si>
+    <t>LTG060</t>
+  </si>
+  <si>
+    <t>KKL006</t>
+  </si>
+  <si>
+    <t>KKL007</t>
+  </si>
+  <si>
+    <t>KKL008</t>
+  </si>
+  <si>
+    <t>KKL009</t>
   </si>
 </sst>
 </file>
@@ -2067,7 +2120,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{35C873EE-46C2-4AAA-9385-A8FDFAFB90AE}">
-  <dimension ref="B2:G234"/>
+  <dimension ref="B2:G251"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="2" max="2" width="9.5" bestFit="1" customWidth="1"/>
@@ -2484,318 +2537,267 @@
     </row>
     <row r="31" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B31" s="2" t="s">
-        <v>443</v>
+        <v>451</v>
       </c>
       <c r="C31" t="s">
-        <v>40</v>
+        <v>22</v>
       </c>
       <c r="D31" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="E31" s="2" t="s">
-        <v>447</v>
-      </c>
+      <c r="E31" s="2"/>
     </row>
     <row r="32" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B32" s="2" t="s">
-        <v>444</v>
+        <v>452</v>
       </c>
       <c r="C32" t="s">
-        <v>40</v>
+        <v>19</v>
       </c>
       <c r="D32" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="E32" s="2" t="s">
-        <v>448</v>
-      </c>
-    </row>
-    <row r="33" spans="2:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="E32" s="2"/>
+    </row>
+    <row r="33" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B33" s="2" t="s">
-        <v>445</v>
+        <v>453</v>
       </c>
       <c r="C33" t="s">
-        <v>40</v>
+        <v>19</v>
       </c>
       <c r="D33" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="E33" s="2" t="s">
-        <v>449</v>
-      </c>
-    </row>
-    <row r="34" spans="2:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="E33" s="2"/>
+    </row>
+    <row r="34" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B34" s="2" t="s">
-        <v>446</v>
+        <v>454</v>
       </c>
       <c r="C34" t="s">
-        <v>40</v>
+        <v>19</v>
       </c>
       <c r="D34" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="E34" s="2" t="s">
+      <c r="E34" s="2"/>
+    </row>
+    <row r="35" spans="2:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="B35" s="2" t="s">
+        <v>455</v>
+      </c>
+      <c r="C35" t="s">
+        <v>19</v>
+      </c>
+      <c r="D35" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E35" s="2"/>
+    </row>
+    <row r="36" spans="2:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="B36" s="2" t="s">
+        <v>456</v>
+      </c>
+      <c r="C36" t="s">
+        <v>22</v>
+      </c>
+      <c r="D36" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E36" s="2"/>
+    </row>
+    <row r="37" spans="2:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="B37" s="2" t="s">
+        <v>457</v>
+      </c>
+      <c r="C37" t="s">
+        <v>22</v>
+      </c>
+      <c r="D37" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E37" s="2"/>
+    </row>
+    <row r="38" spans="2:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="B38" s="2" t="s">
+        <v>458</v>
+      </c>
+      <c r="C38" t="s">
+        <v>40</v>
+      </c>
+      <c r="D38" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E38" s="2"/>
+    </row>
+    <row r="39" spans="2:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="B39" s="2" t="s">
+        <v>459</v>
+      </c>
+      <c r="C39" t="s">
+        <v>19</v>
+      </c>
+      <c r="D39" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E39" s="2"/>
+    </row>
+    <row r="40" spans="2:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="B40" s="2" t="s">
+        <v>460</v>
+      </c>
+      <c r="C40" t="s">
+        <v>19</v>
+      </c>
+      <c r="D40" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E40" s="2"/>
+    </row>
+    <row r="41" spans="2:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="B41" s="2" t="s">
+        <v>461</v>
+      </c>
+      <c r="C41" t="s">
+        <v>22</v>
+      </c>
+      <c r="D41" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E41" s="2"/>
+    </row>
+    <row r="42" spans="2:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="B42" s="2" t="s">
+        <v>462</v>
+      </c>
+      <c r="C42" t="s">
+        <v>22</v>
+      </c>
+      <c r="D42" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E42" s="2"/>
+    </row>
+    <row r="43" spans="2:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="B43" s="2" t="s">
+        <v>463</v>
+      </c>
+      <c r="C43" t="s">
+        <v>40</v>
+      </c>
+      <c r="D43" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E43" s="2"/>
+    </row>
+    <row r="44" spans="2:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="B44" s="2" t="s">
+        <v>464</v>
+      </c>
+      <c r="C44" t="s">
+        <v>19</v>
+      </c>
+      <c r="D44" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E44" s="2"/>
+    </row>
+    <row r="45" spans="2:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="B45" s="2" t="s">
+        <v>465</v>
+      </c>
+      <c r="C45" t="s">
+        <v>19</v>
+      </c>
+      <c r="D45" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E45" s="2"/>
+    </row>
+    <row r="46" spans="2:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="B46" s="2" t="s">
+        <v>466</v>
+      </c>
+      <c r="C46" t="s">
+        <v>22</v>
+      </c>
+      <c r="D46" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E46" s="2"/>
+    </row>
+    <row r="47" spans="2:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="B47" s="2" t="s">
+        <v>467</v>
+      </c>
+      <c r="C47" t="s">
+        <v>22</v>
+      </c>
+      <c r="D47" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E47" s="2"/>
+    </row>
+    <row r="48" spans="2:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="B48" s="2" t="s">
+        <v>443</v>
+      </c>
+      <c r="C48" t="s">
+        <v>40</v>
+      </c>
+      <c r="D48" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E48" s="2" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="49" spans="2:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="B49" s="2" t="s">
+        <v>444</v>
+      </c>
+      <c r="C49" t="s">
+        <v>40</v>
+      </c>
+      <c r="D49" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E49" s="2" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="50" spans="2:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="B50" s="2" t="s">
+        <v>449</v>
+      </c>
+      <c r="C50" t="s">
+        <v>40</v>
+      </c>
+      <c r="D50" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E50" s="2" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="51" spans="2:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="B51" s="2" t="s">
         <v>450</v>
       </c>
-    </row>
-    <row r="35" spans="2:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="B35" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="C35" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="D35" t="s">
-        <v>62</v>
-      </c>
-      <c r="E35" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="G35" s="1"/>
-    </row>
-    <row r="36" spans="2:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="B36" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="C36" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="D36" t="s">
-        <v>62</v>
-      </c>
-      <c r="E36" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="G36" s="1"/>
-    </row>
-    <row r="37" spans="2:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="B37" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="C37" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="D37" t="s">
-        <v>62</v>
-      </c>
-      <c r="E37" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="G37" s="1"/>
-    </row>
-    <row r="38" spans="2:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="B38" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="C38" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="D38" t="s">
-        <v>62</v>
-      </c>
-      <c r="E38" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="G38" s="1"/>
-    </row>
-    <row r="39" spans="2:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="B39" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="C39" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="D39" t="s">
-        <v>62</v>
-      </c>
-      <c r="E39" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="G39" s="1"/>
-    </row>
-    <row r="40" spans="2:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="B40" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="C40" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="D40" t="s">
-        <v>62</v>
-      </c>
-      <c r="E40" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="G40" s="1"/>
-    </row>
-    <row r="41" spans="2:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="B41" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="C41" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="D41" t="s">
-        <v>62</v>
-      </c>
-      <c r="E41" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="G41" s="1"/>
-    </row>
-    <row r="42" spans="2:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="B42" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="C42" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="D42" t="s">
-        <v>62</v>
-      </c>
-      <c r="E42" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="G42" s="1"/>
-    </row>
-    <row r="43" spans="2:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="B43" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="C43" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="D43" t="s">
-        <v>62</v>
-      </c>
-      <c r="E43" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="G43" s="1"/>
-    </row>
-    <row r="44" spans="2:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="B44" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="C44" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="D44" t="s">
-        <v>62</v>
-      </c>
-      <c r="E44" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="G44" s="1"/>
-    </row>
-    <row r="45" spans="2:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="B45" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="C45" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="D45" t="s">
-        <v>62</v>
-      </c>
-      <c r="E45" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="G45" s="1"/>
-    </row>
-    <row r="46" spans="2:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="B46" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="C46" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="D46" t="s">
-        <v>62</v>
-      </c>
-      <c r="E46" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="G46" s="1"/>
-    </row>
-    <row r="47" spans="2:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="B47" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="C47" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="D47" t="s">
-        <v>62</v>
-      </c>
-      <c r="E47" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="G47" s="1"/>
-    </row>
-    <row r="48" spans="2:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="B48" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="C48" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="D48" t="s">
-        <v>62</v>
-      </c>
-      <c r="E48" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="G48" s="1"/>
-    </row>
-    <row r="49" spans="2:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="B49" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="C49" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="D49" t="s">
-        <v>62</v>
-      </c>
-      <c r="E49" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="G49" s="1"/>
-    </row>
-    <row r="50" spans="2:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="B50" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="C50" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="D50" t="s">
-        <v>62</v>
-      </c>
-      <c r="E50" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="G50" s="1"/>
-    </row>
-    <row r="51" spans="2:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="B51" s="1" t="s">
-        <v>94</v>
-      </c>
-      <c r="C51" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="D51" t="s">
-        <v>62</v>
-      </c>
-      <c r="E51" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="G51" s="1"/>
+      <c r="C51" t="s">
+        <v>40</v>
+      </c>
+      <c r="D51" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E51" s="2" t="s">
+        <v>448</v>
+      </c>
     </row>
     <row r="52" spans="2:7" x14ac:dyDescent="0.55000000000000004">
       <c r="B52" s="1" t="s">
-        <v>96</v>
+        <v>60</v>
       </c>
       <c r="C52" s="1" t="s">
         <v>61</v>
@@ -2804,13 +2806,13 @@
         <v>62</v>
       </c>
       <c r="E52" s="1" t="s">
-        <v>97</v>
+        <v>63</v>
       </c>
       <c r="G52" s="1"/>
     </row>
     <row r="53" spans="2:7" x14ac:dyDescent="0.55000000000000004">
       <c r="B53" s="1" t="s">
-        <v>98</v>
+        <v>64</v>
       </c>
       <c r="C53" s="1" t="s">
         <v>61</v>
@@ -2819,13 +2821,13 @@
         <v>62</v>
       </c>
       <c r="E53" s="1" t="s">
-        <v>99</v>
+        <v>65</v>
       </c>
       <c r="G53" s="1"/>
     </row>
     <row r="54" spans="2:7" x14ac:dyDescent="0.55000000000000004">
       <c r="B54" s="1" t="s">
-        <v>100</v>
+        <v>66</v>
       </c>
       <c r="C54" s="1" t="s">
         <v>61</v>
@@ -2834,13 +2836,13 @@
         <v>62</v>
       </c>
       <c r="E54" s="1" t="s">
-        <v>101</v>
+        <v>67</v>
       </c>
       <c r="G54" s="1"/>
     </row>
     <row r="55" spans="2:7" x14ac:dyDescent="0.55000000000000004">
       <c r="B55" s="1" t="s">
-        <v>102</v>
+        <v>68</v>
       </c>
       <c r="C55" s="1" t="s">
         <v>61</v>
@@ -2849,13 +2851,13 @@
         <v>62</v>
       </c>
       <c r="E55" s="1" t="s">
-        <v>103</v>
+        <v>69</v>
       </c>
       <c r="G55" s="1"/>
     </row>
     <row r="56" spans="2:7" x14ac:dyDescent="0.55000000000000004">
       <c r="B56" s="1" t="s">
-        <v>104</v>
+        <v>70</v>
       </c>
       <c r="C56" s="1" t="s">
         <v>61</v>
@@ -2864,13 +2866,13 @@
         <v>62</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>105</v>
+        <v>71</v>
       </c>
       <c r="G56" s="1"/>
     </row>
     <row r="57" spans="2:7" x14ac:dyDescent="0.55000000000000004">
       <c r="B57" s="1" t="s">
-        <v>106</v>
+        <v>72</v>
       </c>
       <c r="C57" s="1" t="s">
         <v>61</v>
@@ -2879,13 +2881,13 @@
         <v>62</v>
       </c>
       <c r="E57" s="1" t="s">
-        <v>107</v>
+        <v>73</v>
       </c>
       <c r="G57" s="1"/>
     </row>
     <row r="58" spans="2:7" x14ac:dyDescent="0.55000000000000004">
       <c r="B58" s="1" t="s">
-        <v>108</v>
+        <v>74</v>
       </c>
       <c r="C58" s="1" t="s">
         <v>61</v>
@@ -2894,13 +2896,13 @@
         <v>62</v>
       </c>
       <c r="E58" s="1" t="s">
-        <v>109</v>
+        <v>75</v>
       </c>
       <c r="G58" s="1"/>
     </row>
     <row r="59" spans="2:7" x14ac:dyDescent="0.55000000000000004">
       <c r="B59" s="1" t="s">
-        <v>110</v>
+        <v>76</v>
       </c>
       <c r="C59" s="1" t="s">
         <v>61</v>
@@ -2909,13 +2911,13 @@
         <v>62</v>
       </c>
       <c r="E59" s="1" t="s">
-        <v>111</v>
+        <v>77</v>
       </c>
       <c r="G59" s="1"/>
     </row>
     <row r="60" spans="2:7" x14ac:dyDescent="0.55000000000000004">
       <c r="B60" s="1" t="s">
-        <v>112</v>
+        <v>78</v>
       </c>
       <c r="C60" s="1" t="s">
         <v>61</v>
@@ -2924,13 +2926,13 @@
         <v>62</v>
       </c>
       <c r="E60" s="1" t="s">
-        <v>113</v>
+        <v>79</v>
       </c>
       <c r="G60" s="1"/>
     </row>
     <row r="61" spans="2:7" x14ac:dyDescent="0.55000000000000004">
       <c r="B61" s="1" t="s">
-        <v>114</v>
+        <v>80</v>
       </c>
       <c r="C61" s="1" t="s">
         <v>61</v>
@@ -2939,13 +2941,13 @@
         <v>62</v>
       </c>
       <c r="E61" s="1" t="s">
-        <v>115</v>
+        <v>81</v>
       </c>
       <c r="G61" s="1"/>
     </row>
     <row r="62" spans="2:7" x14ac:dyDescent="0.55000000000000004">
       <c r="B62" s="1" t="s">
-        <v>116</v>
+        <v>82</v>
       </c>
       <c r="C62" s="1" t="s">
         <v>61</v>
@@ -2954,13 +2956,13 @@
         <v>62</v>
       </c>
       <c r="E62" s="1" t="s">
-        <v>117</v>
+        <v>83</v>
       </c>
       <c r="G62" s="1"/>
     </row>
     <row r="63" spans="2:7" x14ac:dyDescent="0.55000000000000004">
       <c r="B63" s="1" t="s">
-        <v>118</v>
+        <v>84</v>
       </c>
       <c r="C63" s="1" t="s">
         <v>61</v>
@@ -2969,13 +2971,13 @@
         <v>62</v>
       </c>
       <c r="E63" s="1" t="s">
-        <v>119</v>
+        <v>85</v>
       </c>
       <c r="G63" s="1"/>
     </row>
     <row r="64" spans="2:7" x14ac:dyDescent="0.55000000000000004">
       <c r="B64" s="1" t="s">
-        <v>120</v>
+        <v>86</v>
       </c>
       <c r="C64" s="1" t="s">
         <v>61</v>
@@ -2984,13 +2986,13 @@
         <v>62</v>
       </c>
       <c r="E64" s="1" t="s">
-        <v>121</v>
+        <v>87</v>
       </c>
       <c r="G64" s="1"/>
     </row>
     <row r="65" spans="2:7" x14ac:dyDescent="0.55000000000000004">
       <c r="B65" s="1" t="s">
-        <v>122</v>
+        <v>88</v>
       </c>
       <c r="C65" s="1" t="s">
         <v>61</v>
@@ -2999,268 +3001,268 @@
         <v>62</v>
       </c>
       <c r="E65" s="1" t="s">
-        <v>123</v>
+        <v>89</v>
       </c>
       <c r="G65" s="1"/>
     </row>
     <row r="66" spans="2:7" x14ac:dyDescent="0.55000000000000004">
       <c r="B66" s="1" t="s">
-        <v>124</v>
+        <v>90</v>
       </c>
       <c r="C66" s="1" t="s">
-        <v>125</v>
+        <v>61</v>
       </c>
       <c r="D66" t="s">
         <v>62</v>
       </c>
       <c r="E66" s="1" t="s">
-        <v>126</v>
+        <v>91</v>
       </c>
       <c r="G66" s="1"/>
     </row>
     <row r="67" spans="2:7" x14ac:dyDescent="0.55000000000000004">
       <c r="B67" s="1" t="s">
-        <v>127</v>
+        <v>92</v>
       </c>
       <c r="C67" s="1" t="s">
-        <v>125</v>
+        <v>61</v>
       </c>
       <c r="D67" t="s">
         <v>62</v>
       </c>
       <c r="E67" s="1" t="s">
-        <v>128</v>
+        <v>93</v>
       </c>
       <c r="G67" s="1"/>
     </row>
     <row r="68" spans="2:7" x14ac:dyDescent="0.55000000000000004">
       <c r="B68" s="1" t="s">
-        <v>129</v>
+        <v>94</v>
       </c>
       <c r="C68" s="1" t="s">
-        <v>125</v>
+        <v>61</v>
       </c>
       <c r="D68" t="s">
         <v>62</v>
       </c>
       <c r="E68" s="1" t="s">
-        <v>130</v>
+        <v>95</v>
       </c>
       <c r="G68" s="1"/>
     </row>
     <row r="69" spans="2:7" x14ac:dyDescent="0.55000000000000004">
       <c r="B69" s="1" t="s">
-        <v>131</v>
+        <v>96</v>
       </c>
       <c r="C69" s="1" t="s">
-        <v>125</v>
+        <v>61</v>
       </c>
       <c r="D69" t="s">
         <v>62</v>
       </c>
       <c r="E69" s="1" t="s">
-        <v>132</v>
+        <v>97</v>
       </c>
       <c r="G69" s="1"/>
     </row>
     <row r="70" spans="2:7" x14ac:dyDescent="0.55000000000000004">
       <c r="B70" s="1" t="s">
-        <v>133</v>
+        <v>98</v>
       </c>
       <c r="C70" s="1" t="s">
-        <v>125</v>
+        <v>61</v>
       </c>
       <c r="D70" t="s">
         <v>62</v>
       </c>
       <c r="E70" s="1" t="s">
-        <v>134</v>
+        <v>99</v>
       </c>
       <c r="G70" s="1"/>
     </row>
     <row r="71" spans="2:7" x14ac:dyDescent="0.55000000000000004">
       <c r="B71" s="1" t="s">
-        <v>135</v>
+        <v>100</v>
       </c>
       <c r="C71" s="1" t="s">
-        <v>125</v>
+        <v>61</v>
       </c>
       <c r="D71" t="s">
         <v>62</v>
       </c>
       <c r="E71" s="1" t="s">
-        <v>136</v>
+        <v>101</v>
       </c>
       <c r="G71" s="1"/>
     </row>
     <row r="72" spans="2:7" x14ac:dyDescent="0.55000000000000004">
       <c r="B72" s="1" t="s">
-        <v>137</v>
+        <v>102</v>
       </c>
       <c r="C72" s="1" t="s">
-        <v>125</v>
+        <v>61</v>
       </c>
       <c r="D72" t="s">
         <v>62</v>
       </c>
       <c r="E72" s="1" t="s">
-        <v>138</v>
+        <v>103</v>
       </c>
       <c r="G72" s="1"/>
     </row>
     <row r="73" spans="2:7" x14ac:dyDescent="0.55000000000000004">
       <c r="B73" s="1" t="s">
-        <v>139</v>
+        <v>104</v>
       </c>
       <c r="C73" s="1" t="s">
-        <v>125</v>
+        <v>61</v>
       </c>
       <c r="D73" t="s">
         <v>62</v>
       </c>
       <c r="E73" s="1" t="s">
-        <v>140</v>
+        <v>105</v>
       </c>
       <c r="G73" s="1"/>
     </row>
     <row r="74" spans="2:7" x14ac:dyDescent="0.55000000000000004">
       <c r="B74" s="1" t="s">
-        <v>141</v>
+        <v>106</v>
       </c>
       <c r="C74" s="1" t="s">
-        <v>125</v>
+        <v>61</v>
       </c>
       <c r="D74" t="s">
         <v>62</v>
       </c>
       <c r="E74" s="1" t="s">
-        <v>142</v>
+        <v>107</v>
       </c>
       <c r="G74" s="1"/>
     </row>
     <row r="75" spans="2:7" x14ac:dyDescent="0.55000000000000004">
       <c r="B75" s="1" t="s">
-        <v>143</v>
+        <v>108</v>
       </c>
       <c r="C75" s="1" t="s">
-        <v>125</v>
+        <v>61</v>
       </c>
       <c r="D75" t="s">
         <v>62</v>
       </c>
       <c r="E75" s="1" t="s">
-        <v>144</v>
+        <v>109</v>
       </c>
       <c r="G75" s="1"/>
     </row>
     <row r="76" spans="2:7" x14ac:dyDescent="0.55000000000000004">
       <c r="B76" s="1" t="s">
-        <v>145</v>
+        <v>110</v>
       </c>
       <c r="C76" s="1" t="s">
-        <v>125</v>
+        <v>61</v>
       </c>
       <c r="D76" t="s">
         <v>62</v>
       </c>
       <c r="E76" s="1" t="s">
-        <v>146</v>
+        <v>111</v>
       </c>
       <c r="G76" s="1"/>
     </row>
     <row r="77" spans="2:7" x14ac:dyDescent="0.55000000000000004">
       <c r="B77" s="1" t="s">
-        <v>147</v>
+        <v>112</v>
       </c>
       <c r="C77" s="1" t="s">
-        <v>125</v>
+        <v>61</v>
       </c>
       <c r="D77" t="s">
         <v>62</v>
       </c>
       <c r="E77" s="1" t="s">
-        <v>148</v>
+        <v>113</v>
       </c>
       <c r="G77" s="1"/>
     </row>
     <row r="78" spans="2:7" x14ac:dyDescent="0.55000000000000004">
       <c r="B78" s="1" t="s">
-        <v>149</v>
+        <v>114</v>
       </c>
       <c r="C78" s="1" t="s">
-        <v>125</v>
+        <v>61</v>
       </c>
       <c r="D78" t="s">
         <v>62</v>
       </c>
       <c r="E78" s="1" t="s">
-        <v>150</v>
+        <v>115</v>
       </c>
       <c r="G78" s="1"/>
     </row>
     <row r="79" spans="2:7" x14ac:dyDescent="0.55000000000000004">
       <c r="B79" s="1" t="s">
-        <v>151</v>
+        <v>116</v>
       </c>
       <c r="C79" s="1" t="s">
-        <v>125</v>
+        <v>61</v>
       </c>
       <c r="D79" t="s">
         <v>62</v>
       </c>
       <c r="E79" s="1" t="s">
-        <v>152</v>
+        <v>117</v>
       </c>
       <c r="G79" s="1"/>
     </row>
     <row r="80" spans="2:7" x14ac:dyDescent="0.55000000000000004">
       <c r="B80" s="1" t="s">
-        <v>153</v>
+        <v>118</v>
       </c>
       <c r="C80" s="1" t="s">
-        <v>125</v>
+        <v>61</v>
       </c>
       <c r="D80" t="s">
         <v>62</v>
       </c>
       <c r="E80" s="1" t="s">
-        <v>154</v>
+        <v>119</v>
       </c>
       <c r="G80" s="1"/>
     </row>
     <row r="81" spans="2:7" x14ac:dyDescent="0.55000000000000004">
       <c r="B81" s="1" t="s">
-        <v>155</v>
+        <v>120</v>
       </c>
       <c r="C81" s="1" t="s">
-        <v>125</v>
+        <v>61</v>
       </c>
       <c r="D81" t="s">
         <v>62</v>
       </c>
       <c r="E81" s="1" t="s">
-        <v>156</v>
+        <v>121</v>
       </c>
       <c r="G81" s="1"/>
     </row>
     <row r="82" spans="2:7" x14ac:dyDescent="0.55000000000000004">
       <c r="B82" s="1" t="s">
-        <v>157</v>
+        <v>122</v>
       </c>
       <c r="C82" s="1" t="s">
-        <v>125</v>
+        <v>61</v>
       </c>
       <c r="D82" t="s">
         <v>62</v>
       </c>
       <c r="E82" s="1" t="s">
-        <v>158</v>
+        <v>123</v>
       </c>
       <c r="G82" s="1"/>
     </row>
     <row r="83" spans="2:7" x14ac:dyDescent="0.55000000000000004">
       <c r="B83" s="1" t="s">
-        <v>159</v>
+        <v>124</v>
       </c>
       <c r="C83" s="1" t="s">
         <v>125</v>
@@ -3269,13 +3271,13 @@
         <v>62</v>
       </c>
       <c r="E83" s="1" t="s">
-        <v>160</v>
+        <v>126</v>
       </c>
       <c r="G83" s="1"/>
     </row>
     <row r="84" spans="2:7" x14ac:dyDescent="0.55000000000000004">
       <c r="B84" s="1" t="s">
-        <v>161</v>
+        <v>127</v>
       </c>
       <c r="C84" s="1" t="s">
         <v>125</v>
@@ -3284,13 +3286,13 @@
         <v>62</v>
       </c>
       <c r="E84" s="1" t="s">
-        <v>162</v>
+        <v>128</v>
       </c>
       <c r="G84" s="1"/>
     </row>
     <row r="85" spans="2:7" x14ac:dyDescent="0.55000000000000004">
       <c r="B85" s="1" t="s">
-        <v>163</v>
+        <v>129</v>
       </c>
       <c r="C85" s="1" t="s">
         <v>125</v>
@@ -3299,13 +3301,13 @@
         <v>62</v>
       </c>
       <c r="E85" s="1" t="s">
-        <v>164</v>
+        <v>130</v>
       </c>
       <c r="G85" s="1"/>
     </row>
     <row r="86" spans="2:7" x14ac:dyDescent="0.55000000000000004">
       <c r="B86" s="1" t="s">
-        <v>165</v>
+        <v>131</v>
       </c>
       <c r="C86" s="1" t="s">
         <v>125</v>
@@ -3314,13 +3316,13 @@
         <v>62</v>
       </c>
       <c r="E86" s="1" t="s">
-        <v>166</v>
+        <v>132</v>
       </c>
       <c r="G86" s="1"/>
     </row>
     <row r="87" spans="2:7" x14ac:dyDescent="0.55000000000000004">
       <c r="B87" s="1" t="s">
-        <v>167</v>
+        <v>133</v>
       </c>
       <c r="C87" s="1" t="s">
         <v>125</v>
@@ -3329,13 +3331,13 @@
         <v>62</v>
       </c>
       <c r="E87" s="1" t="s">
-        <v>168</v>
+        <v>134</v>
       </c>
       <c r="G87" s="1"/>
     </row>
     <row r="88" spans="2:7" x14ac:dyDescent="0.55000000000000004">
       <c r="B88" s="1" t="s">
-        <v>169</v>
+        <v>135</v>
       </c>
       <c r="C88" s="1" t="s">
         <v>125</v>
@@ -3344,13 +3346,13 @@
         <v>62</v>
       </c>
       <c r="E88" s="1" t="s">
-        <v>170</v>
+        <v>136</v>
       </c>
       <c r="G88" s="1"/>
     </row>
     <row r="89" spans="2:7" x14ac:dyDescent="0.55000000000000004">
       <c r="B89" s="1" t="s">
-        <v>171</v>
+        <v>137</v>
       </c>
       <c r="C89" s="1" t="s">
         <v>125</v>
@@ -3359,13 +3361,13 @@
         <v>62</v>
       </c>
       <c r="E89" s="1" t="s">
-        <v>172</v>
+        <v>138</v>
       </c>
       <c r="G89" s="1"/>
     </row>
     <row r="90" spans="2:7" x14ac:dyDescent="0.55000000000000004">
       <c r="B90" s="1" t="s">
-        <v>173</v>
+        <v>139</v>
       </c>
       <c r="C90" s="1" t="s">
         <v>125</v>
@@ -3374,13 +3376,13 @@
         <v>62</v>
       </c>
       <c r="E90" s="1" t="s">
-        <v>174</v>
+        <v>140</v>
       </c>
       <c r="G90" s="1"/>
     </row>
     <row r="91" spans="2:7" x14ac:dyDescent="0.55000000000000004">
       <c r="B91" s="1" t="s">
-        <v>175</v>
+        <v>141</v>
       </c>
       <c r="C91" s="1" t="s">
         <v>125</v>
@@ -3389,13 +3391,13 @@
         <v>62</v>
       </c>
       <c r="E91" s="1" t="s">
-        <v>176</v>
+        <v>142</v>
       </c>
       <c r="G91" s="1"/>
     </row>
     <row r="92" spans="2:7" x14ac:dyDescent="0.55000000000000004">
       <c r="B92" s="1" t="s">
-        <v>177</v>
+        <v>143</v>
       </c>
       <c r="C92" s="1" t="s">
         <v>125</v>
@@ -3404,13 +3406,13 @@
         <v>62</v>
       </c>
       <c r="E92" s="1" t="s">
-        <v>178</v>
+        <v>144</v>
       </c>
       <c r="G92" s="1"/>
     </row>
     <row r="93" spans="2:7" x14ac:dyDescent="0.55000000000000004">
       <c r="B93" s="1" t="s">
-        <v>179</v>
+        <v>145</v>
       </c>
       <c r="C93" s="1" t="s">
         <v>125</v>
@@ -3419,13 +3421,13 @@
         <v>62</v>
       </c>
       <c r="E93" s="1" t="s">
-        <v>180</v>
+        <v>146</v>
       </c>
       <c r="G93" s="1"/>
     </row>
     <row r="94" spans="2:7" x14ac:dyDescent="0.55000000000000004">
       <c r="B94" s="1" t="s">
-        <v>181</v>
+        <v>147</v>
       </c>
       <c r="C94" s="1" t="s">
         <v>125</v>
@@ -3434,13 +3436,13 @@
         <v>62</v>
       </c>
       <c r="E94" s="1" t="s">
-        <v>182</v>
+        <v>148</v>
       </c>
       <c r="G94" s="1"/>
     </row>
     <row r="95" spans="2:7" x14ac:dyDescent="0.55000000000000004">
       <c r="B95" s="1" t="s">
-        <v>183</v>
+        <v>149</v>
       </c>
       <c r="C95" s="1" t="s">
         <v>125</v>
@@ -3449,13 +3451,13 @@
         <v>62</v>
       </c>
       <c r="E95" s="1" t="s">
-        <v>184</v>
+        <v>150</v>
       </c>
       <c r="G95" s="1"/>
     </row>
     <row r="96" spans="2:7" x14ac:dyDescent="0.55000000000000004">
       <c r="B96" s="1" t="s">
-        <v>185</v>
+        <v>151</v>
       </c>
       <c r="C96" s="1" t="s">
         <v>125</v>
@@ -3464,13 +3466,13 @@
         <v>62</v>
       </c>
       <c r="E96" s="1" t="s">
-        <v>186</v>
+        <v>152</v>
       </c>
       <c r="G96" s="1"/>
     </row>
     <row r="97" spans="2:7" x14ac:dyDescent="0.55000000000000004">
       <c r="B97" s="1" t="s">
-        <v>187</v>
+        <v>153</v>
       </c>
       <c r="C97" s="1" t="s">
         <v>125</v>
@@ -3479,13 +3481,13 @@
         <v>62</v>
       </c>
       <c r="E97" s="1" t="s">
-        <v>188</v>
+        <v>154</v>
       </c>
       <c r="G97" s="1"/>
     </row>
     <row r="98" spans="2:7" x14ac:dyDescent="0.55000000000000004">
       <c r="B98" s="1" t="s">
-        <v>189</v>
+        <v>155</v>
       </c>
       <c r="C98" s="1" t="s">
         <v>125</v>
@@ -3494,13 +3496,13 @@
         <v>62</v>
       </c>
       <c r="E98" s="1" t="s">
-        <v>190</v>
+        <v>156</v>
       </c>
       <c r="G98" s="1"/>
     </row>
     <row r="99" spans="2:7" x14ac:dyDescent="0.55000000000000004">
       <c r="B99" s="1" t="s">
-        <v>191</v>
+        <v>157</v>
       </c>
       <c r="C99" s="1" t="s">
         <v>125</v>
@@ -3509,13 +3511,13 @@
         <v>62</v>
       </c>
       <c r="E99" s="1" t="s">
-        <v>192</v>
+        <v>158</v>
       </c>
       <c r="G99" s="1"/>
     </row>
     <row r="100" spans="2:7" x14ac:dyDescent="0.55000000000000004">
       <c r="B100" s="1" t="s">
-        <v>193</v>
+        <v>159</v>
       </c>
       <c r="C100" s="1" t="s">
         <v>125</v>
@@ -3524,13 +3526,13 @@
         <v>62</v>
       </c>
       <c r="E100" s="1" t="s">
-        <v>194</v>
+        <v>160</v>
       </c>
       <c r="G100" s="1"/>
     </row>
     <row r="101" spans="2:7" x14ac:dyDescent="0.55000000000000004">
       <c r="B101" s="1" t="s">
-        <v>195</v>
+        <v>161</v>
       </c>
       <c r="C101" s="1" t="s">
         <v>125</v>
@@ -3539,13 +3541,13 @@
         <v>62</v>
       </c>
       <c r="E101" s="1" t="s">
-        <v>196</v>
+        <v>162</v>
       </c>
       <c r="G101" s="1"/>
     </row>
     <row r="102" spans="2:7" x14ac:dyDescent="0.55000000000000004">
       <c r="B102" s="1" t="s">
-        <v>197</v>
+        <v>163</v>
       </c>
       <c r="C102" s="1" t="s">
         <v>125</v>
@@ -3554,13 +3556,13 @@
         <v>62</v>
       </c>
       <c r="E102" s="1" t="s">
-        <v>198</v>
+        <v>164</v>
       </c>
       <c r="G102" s="1"/>
     </row>
     <row r="103" spans="2:7" x14ac:dyDescent="0.55000000000000004">
       <c r="B103" s="1" t="s">
-        <v>199</v>
+        <v>165</v>
       </c>
       <c r="C103" s="1" t="s">
         <v>125</v>
@@ -3569,13 +3571,13 @@
         <v>62</v>
       </c>
       <c r="E103" s="1" t="s">
-        <v>200</v>
+        <v>166</v>
       </c>
       <c r="G103" s="1"/>
     </row>
     <row r="104" spans="2:7" x14ac:dyDescent="0.55000000000000004">
       <c r="B104" s="1" t="s">
-        <v>201</v>
+        <v>167</v>
       </c>
       <c r="C104" s="1" t="s">
         <v>125</v>
@@ -3584,13 +3586,13 @@
         <v>62</v>
       </c>
       <c r="E104" s="1" t="s">
-        <v>202</v>
+        <v>168</v>
       </c>
       <c r="G104" s="1"/>
     </row>
     <row r="105" spans="2:7" x14ac:dyDescent="0.55000000000000004">
       <c r="B105" s="1" t="s">
-        <v>203</v>
+        <v>169</v>
       </c>
       <c r="C105" s="1" t="s">
         <v>125</v>
@@ -3599,13 +3601,13 @@
         <v>62</v>
       </c>
       <c r="E105" s="1" t="s">
-        <v>204</v>
+        <v>170</v>
       </c>
       <c r="G105" s="1"/>
     </row>
     <row r="106" spans="2:7" x14ac:dyDescent="0.55000000000000004">
       <c r="B106" s="1" t="s">
-        <v>205</v>
+        <v>171</v>
       </c>
       <c r="C106" s="1" t="s">
         <v>125</v>
@@ -3614,13 +3616,13 @@
         <v>62</v>
       </c>
       <c r="E106" s="1" t="s">
-        <v>206</v>
+        <v>172</v>
       </c>
       <c r="G106" s="1"/>
     </row>
     <row r="107" spans="2:7" x14ac:dyDescent="0.55000000000000004">
       <c r="B107" s="1" t="s">
-        <v>207</v>
+        <v>173</v>
       </c>
       <c r="C107" s="1" t="s">
         <v>125</v>
@@ -3629,268 +3631,268 @@
         <v>62</v>
       </c>
       <c r="E107" s="1" t="s">
-        <v>208</v>
+        <v>174</v>
       </c>
       <c r="G107" s="1"/>
     </row>
     <row r="108" spans="2:7" x14ac:dyDescent="0.55000000000000004">
       <c r="B108" s="1" t="s">
-        <v>209</v>
+        <v>175</v>
       </c>
       <c r="C108" s="1" t="s">
-        <v>210</v>
+        <v>125</v>
       </c>
       <c r="D108" t="s">
         <v>62</v>
       </c>
       <c r="E108" s="1" t="s">
-        <v>211</v>
+        <v>176</v>
       </c>
       <c r="G108" s="1"/>
     </row>
     <row r="109" spans="2:7" x14ac:dyDescent="0.55000000000000004">
       <c r="B109" s="1" t="s">
-        <v>212</v>
+        <v>177</v>
       </c>
       <c r="C109" s="1" t="s">
-        <v>210</v>
+        <v>125</v>
       </c>
       <c r="D109" t="s">
         <v>62</v>
       </c>
       <c r="E109" s="1" t="s">
-        <v>213</v>
+        <v>178</v>
       </c>
       <c r="G109" s="1"/>
     </row>
     <row r="110" spans="2:7" x14ac:dyDescent="0.55000000000000004">
       <c r="B110" s="1" t="s">
-        <v>214</v>
+        <v>179</v>
       </c>
       <c r="C110" s="1" t="s">
-        <v>210</v>
+        <v>125</v>
       </c>
       <c r="D110" t="s">
         <v>62</v>
       </c>
       <c r="E110" s="1" t="s">
-        <v>215</v>
+        <v>180</v>
       </c>
       <c r="G110" s="1"/>
     </row>
     <row r="111" spans="2:7" x14ac:dyDescent="0.55000000000000004">
       <c r="B111" s="1" t="s">
-        <v>216</v>
+        <v>181</v>
       </c>
       <c r="C111" s="1" t="s">
-        <v>210</v>
+        <v>125</v>
       </c>
       <c r="D111" t="s">
         <v>62</v>
       </c>
       <c r="E111" s="1" t="s">
-        <v>217</v>
+        <v>182</v>
       </c>
       <c r="G111" s="1"/>
     </row>
     <row r="112" spans="2:7" x14ac:dyDescent="0.55000000000000004">
       <c r="B112" s="1" t="s">
-        <v>218</v>
+        <v>183</v>
       </c>
       <c r="C112" s="1" t="s">
-        <v>210</v>
+        <v>125</v>
       </c>
       <c r="D112" t="s">
         <v>62</v>
       </c>
       <c r="E112" s="1" t="s">
-        <v>219</v>
+        <v>184</v>
       </c>
       <c r="G112" s="1"/>
     </row>
     <row r="113" spans="2:7" x14ac:dyDescent="0.55000000000000004">
       <c r="B113" s="1" t="s">
-        <v>220</v>
+        <v>185</v>
       </c>
       <c r="C113" s="1" t="s">
-        <v>210</v>
+        <v>125</v>
       </c>
       <c r="D113" t="s">
         <v>62</v>
       </c>
       <c r="E113" s="1" t="s">
-        <v>221</v>
+        <v>186</v>
       </c>
       <c r="G113" s="1"/>
     </row>
     <row r="114" spans="2:7" x14ac:dyDescent="0.55000000000000004">
       <c r="B114" s="1" t="s">
-        <v>222</v>
+        <v>187</v>
       </c>
       <c r="C114" s="1" t="s">
-        <v>210</v>
+        <v>125</v>
       </c>
       <c r="D114" t="s">
         <v>62</v>
       </c>
       <c r="E114" s="1" t="s">
-        <v>223</v>
+        <v>188</v>
       </c>
       <c r="G114" s="1"/>
     </row>
     <row r="115" spans="2:7" x14ac:dyDescent="0.55000000000000004">
       <c r="B115" s="1" t="s">
-        <v>224</v>
+        <v>189</v>
       </c>
       <c r="C115" s="1" t="s">
-        <v>210</v>
+        <v>125</v>
       </c>
       <c r="D115" t="s">
         <v>62</v>
       </c>
       <c r="E115" s="1" t="s">
-        <v>225</v>
+        <v>190</v>
       </c>
       <c r="G115" s="1"/>
     </row>
     <row r="116" spans="2:7" x14ac:dyDescent="0.55000000000000004">
       <c r="B116" s="1" t="s">
-        <v>226</v>
+        <v>191</v>
       </c>
       <c r="C116" s="1" t="s">
-        <v>210</v>
+        <v>125</v>
       </c>
       <c r="D116" t="s">
         <v>62</v>
       </c>
       <c r="E116" s="1" t="s">
-        <v>227</v>
+        <v>192</v>
       </c>
       <c r="G116" s="1"/>
     </row>
     <row r="117" spans="2:7" x14ac:dyDescent="0.55000000000000004">
       <c r="B117" s="1" t="s">
-        <v>228</v>
+        <v>193</v>
       </c>
       <c r="C117" s="1" t="s">
-        <v>210</v>
+        <v>125</v>
       </c>
       <c r="D117" t="s">
         <v>62</v>
       </c>
       <c r="E117" s="1" t="s">
-        <v>229</v>
+        <v>194</v>
       </c>
       <c r="G117" s="1"/>
     </row>
     <row r="118" spans="2:7" x14ac:dyDescent="0.55000000000000004">
       <c r="B118" s="1" t="s">
-        <v>230</v>
+        <v>195</v>
       </c>
       <c r="C118" s="1" t="s">
-        <v>210</v>
+        <v>125</v>
       </c>
       <c r="D118" t="s">
         <v>62</v>
       </c>
       <c r="E118" s="1" t="s">
-        <v>231</v>
+        <v>196</v>
       </c>
       <c r="G118" s="1"/>
     </row>
     <row r="119" spans="2:7" x14ac:dyDescent="0.55000000000000004">
       <c r="B119" s="1" t="s">
-        <v>232</v>
+        <v>197</v>
       </c>
       <c r="C119" s="1" t="s">
-        <v>210</v>
+        <v>125</v>
       </c>
       <c r="D119" t="s">
         <v>62</v>
       </c>
       <c r="E119" s="1" t="s">
-        <v>233</v>
+        <v>198</v>
       </c>
       <c r="G119" s="1"/>
     </row>
     <row r="120" spans="2:7" x14ac:dyDescent="0.55000000000000004">
       <c r="B120" s="1" t="s">
-        <v>234</v>
+        <v>199</v>
       </c>
       <c r="C120" s="1" t="s">
-        <v>210</v>
+        <v>125</v>
       </c>
       <c r="D120" t="s">
         <v>62</v>
       </c>
       <c r="E120" s="1" t="s">
-        <v>235</v>
+        <v>200</v>
       </c>
       <c r="G120" s="1"/>
     </row>
     <row r="121" spans="2:7" x14ac:dyDescent="0.55000000000000004">
       <c r="B121" s="1" t="s">
-        <v>236</v>
+        <v>201</v>
       </c>
       <c r="C121" s="1" t="s">
-        <v>210</v>
+        <v>125</v>
       </c>
       <c r="D121" t="s">
         <v>62</v>
       </c>
       <c r="E121" s="1" t="s">
-        <v>95</v>
+        <v>202</v>
       </c>
       <c r="G121" s="1"/>
     </row>
     <row r="122" spans="2:7" x14ac:dyDescent="0.55000000000000004">
       <c r="B122" s="1" t="s">
-        <v>237</v>
+        <v>203</v>
       </c>
       <c r="C122" s="1" t="s">
-        <v>210</v>
+        <v>125</v>
       </c>
       <c r="D122" t="s">
         <v>62</v>
       </c>
       <c r="E122" s="1" t="s">
-        <v>97</v>
+        <v>204</v>
       </c>
       <c r="G122" s="1"/>
     </row>
     <row r="123" spans="2:7" x14ac:dyDescent="0.55000000000000004">
       <c r="B123" s="1" t="s">
-        <v>238</v>
+        <v>205</v>
       </c>
       <c r="C123" s="1" t="s">
-        <v>210</v>
+        <v>125</v>
       </c>
       <c r="D123" t="s">
         <v>62</v>
       </c>
       <c r="E123" s="1" t="s">
-        <v>99</v>
+        <v>206</v>
       </c>
       <c r="G123" s="1"/>
     </row>
     <row r="124" spans="2:7" x14ac:dyDescent="0.55000000000000004">
       <c r="B124" s="1" t="s">
-        <v>239</v>
+        <v>207</v>
       </c>
       <c r="C124" s="1" t="s">
-        <v>210</v>
+        <v>125</v>
       </c>
       <c r="D124" t="s">
         <v>62</v>
       </c>
       <c r="E124" s="1" t="s">
-        <v>101</v>
+        <v>208</v>
       </c>
       <c r="G124" s="1"/>
     </row>
     <row r="125" spans="2:7" x14ac:dyDescent="0.55000000000000004">
       <c r="B125" s="1" t="s">
-        <v>240</v>
+        <v>209</v>
       </c>
       <c r="C125" s="1" t="s">
         <v>210</v>
@@ -3899,268 +3901,268 @@
         <v>62</v>
       </c>
       <c r="E125" s="1" t="s">
-        <v>103</v>
+        <v>211</v>
       </c>
       <c r="G125" s="1"/>
     </row>
     <row r="126" spans="2:7" x14ac:dyDescent="0.55000000000000004">
       <c r="B126" s="1" t="s">
-        <v>241</v>
+        <v>212</v>
       </c>
       <c r="C126" s="1" t="s">
-        <v>242</v>
+        <v>210</v>
       </c>
       <c r="D126" t="s">
         <v>62</v>
       </c>
       <c r="E126" s="1" t="s">
-        <v>243</v>
+        <v>213</v>
       </c>
       <c r="G126" s="1"/>
     </row>
     <row r="127" spans="2:7" x14ac:dyDescent="0.55000000000000004">
       <c r="B127" s="1" t="s">
-        <v>244</v>
+        <v>214</v>
       </c>
       <c r="C127" s="1" t="s">
-        <v>242</v>
+        <v>210</v>
       </c>
       <c r="D127" t="s">
         <v>62</v>
       </c>
       <c r="E127" s="1" t="s">
-        <v>245</v>
+        <v>215</v>
       </c>
       <c r="G127" s="1"/>
     </row>
     <row r="128" spans="2:7" x14ac:dyDescent="0.55000000000000004">
       <c r="B128" s="1" t="s">
-        <v>246</v>
+        <v>216</v>
       </c>
       <c r="C128" s="1" t="s">
-        <v>242</v>
+        <v>210</v>
       </c>
       <c r="D128" t="s">
         <v>62</v>
       </c>
       <c r="E128" s="1" t="s">
-        <v>247</v>
+        <v>217</v>
       </c>
       <c r="G128" s="1"/>
     </row>
     <row r="129" spans="2:7" x14ac:dyDescent="0.55000000000000004">
       <c r="B129" s="1" t="s">
-        <v>248</v>
+        <v>218</v>
       </c>
       <c r="C129" s="1" t="s">
-        <v>242</v>
+        <v>210</v>
       </c>
       <c r="D129" t="s">
         <v>62</v>
       </c>
       <c r="E129" s="1" t="s">
-        <v>249</v>
+        <v>219</v>
       </c>
       <c r="G129" s="1"/>
     </row>
     <row r="130" spans="2:7" x14ac:dyDescent="0.55000000000000004">
       <c r="B130" s="1" t="s">
-        <v>250</v>
+        <v>220</v>
       </c>
       <c r="C130" s="1" t="s">
-        <v>242</v>
+        <v>210</v>
       </c>
       <c r="D130" t="s">
         <v>62</v>
       </c>
       <c r="E130" s="1" t="s">
-        <v>251</v>
+        <v>221</v>
       </c>
       <c r="G130" s="1"/>
     </row>
     <row r="131" spans="2:7" x14ac:dyDescent="0.55000000000000004">
       <c r="B131" s="1" t="s">
-        <v>252</v>
+        <v>222</v>
       </c>
       <c r="C131" s="1" t="s">
-        <v>242</v>
+        <v>210</v>
       </c>
       <c r="D131" t="s">
         <v>62</v>
       </c>
       <c r="E131" s="1" t="s">
-        <v>253</v>
+        <v>223</v>
       </c>
       <c r="G131" s="1"/>
     </row>
     <row r="132" spans="2:7" x14ac:dyDescent="0.55000000000000004">
       <c r="B132" s="1" t="s">
-        <v>254</v>
+        <v>224</v>
       </c>
       <c r="C132" s="1" t="s">
-        <v>242</v>
+        <v>210</v>
       </c>
       <c r="D132" t="s">
         <v>62</v>
       </c>
       <c r="E132" s="1" t="s">
-        <v>255</v>
+        <v>225</v>
       </c>
       <c r="G132" s="1"/>
     </row>
     <row r="133" spans="2:7" x14ac:dyDescent="0.55000000000000004">
       <c r="B133" s="1" t="s">
-        <v>256</v>
+        <v>226</v>
       </c>
       <c r="C133" s="1" t="s">
-        <v>242</v>
+        <v>210</v>
       </c>
       <c r="D133" t="s">
         <v>62</v>
       </c>
       <c r="E133" s="1" t="s">
-        <v>257</v>
+        <v>227</v>
       </c>
       <c r="G133" s="1"/>
     </row>
     <row r="134" spans="2:7" x14ac:dyDescent="0.55000000000000004">
       <c r="B134" s="1" t="s">
-        <v>258</v>
+        <v>228</v>
       </c>
       <c r="C134" s="1" t="s">
-        <v>242</v>
+        <v>210</v>
       </c>
       <c r="D134" t="s">
         <v>62</v>
       </c>
       <c r="E134" s="1" t="s">
-        <v>259</v>
+        <v>229</v>
       </c>
       <c r="G134" s="1"/>
     </row>
     <row r="135" spans="2:7" x14ac:dyDescent="0.55000000000000004">
       <c r="B135" s="1" t="s">
-        <v>260</v>
+        <v>230</v>
       </c>
       <c r="C135" s="1" t="s">
-        <v>242</v>
+        <v>210</v>
       </c>
       <c r="D135" t="s">
         <v>62</v>
       </c>
       <c r="E135" s="1" t="s">
-        <v>261</v>
+        <v>231</v>
       </c>
       <c r="G135" s="1"/>
     </row>
     <row r="136" spans="2:7" x14ac:dyDescent="0.55000000000000004">
       <c r="B136" s="1" t="s">
-        <v>262</v>
+        <v>232</v>
       </c>
       <c r="C136" s="1" t="s">
-        <v>242</v>
+        <v>210</v>
       </c>
       <c r="D136" t="s">
         <v>62</v>
       </c>
       <c r="E136" s="1" t="s">
-        <v>263</v>
+        <v>233</v>
       </c>
       <c r="G136" s="1"/>
     </row>
     <row r="137" spans="2:7" x14ac:dyDescent="0.55000000000000004">
       <c r="B137" s="1" t="s">
-        <v>264</v>
+        <v>234</v>
       </c>
       <c r="C137" s="1" t="s">
-        <v>242</v>
+        <v>210</v>
       </c>
       <c r="D137" t="s">
         <v>62</v>
       </c>
       <c r="E137" s="1" t="s">
-        <v>265</v>
+        <v>235</v>
       </c>
       <c r="G137" s="1"/>
     </row>
     <row r="138" spans="2:7" x14ac:dyDescent="0.55000000000000004">
       <c r="B138" s="1" t="s">
-        <v>266</v>
+        <v>236</v>
       </c>
       <c r="C138" s="1" t="s">
-        <v>242</v>
+        <v>210</v>
       </c>
       <c r="D138" t="s">
         <v>62</v>
       </c>
       <c r="E138" s="1" t="s">
-        <v>267</v>
+        <v>95</v>
       </c>
       <c r="G138" s="1"/>
     </row>
     <row r="139" spans="2:7" x14ac:dyDescent="0.55000000000000004">
       <c r="B139" s="1" t="s">
-        <v>268</v>
+        <v>237</v>
       </c>
       <c r="C139" s="1" t="s">
-        <v>242</v>
+        <v>210</v>
       </c>
       <c r="D139" t="s">
         <v>62</v>
       </c>
       <c r="E139" s="1" t="s">
-        <v>269</v>
+        <v>97</v>
       </c>
       <c r="G139" s="1"/>
     </row>
     <row r="140" spans="2:7" x14ac:dyDescent="0.55000000000000004">
       <c r="B140" s="1" t="s">
-        <v>270</v>
+        <v>238</v>
       </c>
       <c r="C140" s="1" t="s">
-        <v>242</v>
+        <v>210</v>
       </c>
       <c r="D140" t="s">
         <v>62</v>
       </c>
       <c r="E140" s="1" t="s">
-        <v>271</v>
+        <v>99</v>
       </c>
       <c r="G140" s="1"/>
     </row>
     <row r="141" spans="2:7" x14ac:dyDescent="0.55000000000000004">
       <c r="B141" s="1" t="s">
-        <v>272</v>
+        <v>239</v>
       </c>
       <c r="C141" s="1" t="s">
-        <v>242</v>
+        <v>210</v>
       </c>
       <c r="D141" t="s">
         <v>62</v>
       </c>
       <c r="E141" s="1" t="s">
-        <v>273</v>
+        <v>101</v>
       </c>
       <c r="G141" s="1"/>
     </row>
     <row r="142" spans="2:7" x14ac:dyDescent="0.55000000000000004">
       <c r="B142" s="1" t="s">
-        <v>274</v>
+        <v>240</v>
       </c>
       <c r="C142" s="1" t="s">
-        <v>242</v>
+        <v>210</v>
       </c>
       <c r="D142" t="s">
         <v>62</v>
       </c>
       <c r="E142" s="1" t="s">
-        <v>275</v>
+        <v>103</v>
       </c>
       <c r="G142" s="1"/>
     </row>
     <row r="143" spans="2:7" x14ac:dyDescent="0.55000000000000004">
       <c r="B143" s="1" t="s">
-        <v>276</v>
+        <v>241</v>
       </c>
       <c r="C143" s="1" t="s">
         <v>242</v>
@@ -4169,13 +4171,13 @@
         <v>62</v>
       </c>
       <c r="E143" s="1" t="s">
-        <v>277</v>
+        <v>243</v>
       </c>
       <c r="G143" s="1"/>
     </row>
     <row r="144" spans="2:7" x14ac:dyDescent="0.55000000000000004">
       <c r="B144" s="1" t="s">
-        <v>278</v>
+        <v>244</v>
       </c>
       <c r="C144" s="1" t="s">
         <v>242</v>
@@ -4184,13 +4186,13 @@
         <v>62</v>
       </c>
       <c r="E144" s="1" t="s">
-        <v>279</v>
+        <v>245</v>
       </c>
       <c r="G144" s="1"/>
     </row>
     <row r="145" spans="2:7" x14ac:dyDescent="0.55000000000000004">
       <c r="B145" s="1" t="s">
-        <v>280</v>
+        <v>246</v>
       </c>
       <c r="C145" s="1" t="s">
         <v>242</v>
@@ -4199,13 +4201,13 @@
         <v>62</v>
       </c>
       <c r="E145" s="1" t="s">
-        <v>95</v>
+        <v>247</v>
       </c>
       <c r="G145" s="1"/>
     </row>
     <row r="146" spans="2:7" x14ac:dyDescent="0.55000000000000004">
       <c r="B146" s="1" t="s">
-        <v>281</v>
+        <v>248</v>
       </c>
       <c r="C146" s="1" t="s">
         <v>242</v>
@@ -4214,13 +4216,13 @@
         <v>62</v>
       </c>
       <c r="E146" s="1" t="s">
-        <v>97</v>
+        <v>249</v>
       </c>
       <c r="G146" s="1"/>
     </row>
     <row r="147" spans="2:7" x14ac:dyDescent="0.55000000000000004">
       <c r="B147" s="1" t="s">
-        <v>282</v>
+        <v>250</v>
       </c>
       <c r="C147" s="1" t="s">
         <v>242</v>
@@ -4229,13 +4231,13 @@
         <v>62</v>
       </c>
       <c r="E147" s="1" t="s">
-        <v>99</v>
+        <v>251</v>
       </c>
       <c r="G147" s="1"/>
     </row>
     <row r="148" spans="2:7" x14ac:dyDescent="0.55000000000000004">
       <c r="B148" s="1" t="s">
-        <v>283</v>
+        <v>252</v>
       </c>
       <c r="C148" s="1" t="s">
         <v>242</v>
@@ -4244,13 +4246,13 @@
         <v>62</v>
       </c>
       <c r="E148" s="1" t="s">
-        <v>101</v>
+        <v>253</v>
       </c>
       <c r="G148" s="1"/>
     </row>
     <row r="149" spans="2:7" x14ac:dyDescent="0.55000000000000004">
       <c r="B149" s="1" t="s">
-        <v>284</v>
+        <v>254</v>
       </c>
       <c r="C149" s="1" t="s">
         <v>242</v>
@@ -4259,13 +4261,13 @@
         <v>62</v>
       </c>
       <c r="E149" s="1" t="s">
-        <v>103</v>
+        <v>255</v>
       </c>
       <c r="G149" s="1"/>
     </row>
     <row r="150" spans="2:7" x14ac:dyDescent="0.55000000000000004">
       <c r="B150" s="1" t="s">
-        <v>285</v>
+        <v>256</v>
       </c>
       <c r="C150" s="1" t="s">
         <v>242</v>
@@ -4274,13 +4276,13 @@
         <v>62</v>
       </c>
       <c r="E150" s="1" t="s">
-        <v>286</v>
+        <v>257</v>
       </c>
       <c r="G150" s="1"/>
     </row>
     <row r="151" spans="2:7" x14ac:dyDescent="0.55000000000000004">
       <c r="B151" s="1" t="s">
-        <v>287</v>
+        <v>258</v>
       </c>
       <c r="C151" s="1" t="s">
         <v>242</v>
@@ -4289,13 +4291,13 @@
         <v>62</v>
       </c>
       <c r="E151" s="1" t="s">
-        <v>288</v>
+        <v>259</v>
       </c>
       <c r="G151" s="1"/>
     </row>
     <row r="152" spans="2:7" x14ac:dyDescent="0.55000000000000004">
       <c r="B152" s="1" t="s">
-        <v>289</v>
+        <v>260</v>
       </c>
       <c r="C152" s="1" t="s">
         <v>242</v>
@@ -4304,13 +4306,13 @@
         <v>62</v>
       </c>
       <c r="E152" s="1" t="s">
-        <v>290</v>
+        <v>261</v>
       </c>
       <c r="G152" s="1"/>
     </row>
     <row r="153" spans="2:7" x14ac:dyDescent="0.55000000000000004">
       <c r="B153" s="1" t="s">
-        <v>291</v>
+        <v>262</v>
       </c>
       <c r="C153" s="1" t="s">
         <v>242</v>
@@ -4319,13 +4321,13 @@
         <v>62</v>
       </c>
       <c r="E153" s="1" t="s">
-        <v>292</v>
+        <v>263</v>
       </c>
       <c r="G153" s="1"/>
     </row>
     <row r="154" spans="2:7" x14ac:dyDescent="0.55000000000000004">
       <c r="B154" s="1" t="s">
-        <v>293</v>
+        <v>264</v>
       </c>
       <c r="C154" s="1" t="s">
         <v>242</v>
@@ -4334,13 +4336,13 @@
         <v>62</v>
       </c>
       <c r="E154" s="1" t="s">
-        <v>294</v>
+        <v>265</v>
       </c>
       <c r="G154" s="1"/>
     </row>
     <row r="155" spans="2:7" x14ac:dyDescent="0.55000000000000004">
       <c r="B155" s="1" t="s">
-        <v>295</v>
+        <v>266</v>
       </c>
       <c r="C155" s="1" t="s">
         <v>242</v>
@@ -4349,13 +4351,13 @@
         <v>62</v>
       </c>
       <c r="E155" s="1" t="s">
-        <v>296</v>
+        <v>267</v>
       </c>
       <c r="G155" s="1"/>
     </row>
     <row r="156" spans="2:7" x14ac:dyDescent="0.55000000000000004">
       <c r="B156" s="1" t="s">
-        <v>297</v>
+        <v>268</v>
       </c>
       <c r="C156" s="1" t="s">
         <v>242</v>
@@ -4364,13 +4366,13 @@
         <v>62</v>
       </c>
       <c r="E156" s="1" t="s">
-        <v>229</v>
+        <v>269</v>
       </c>
       <c r="G156" s="1"/>
     </row>
     <row r="157" spans="2:7" x14ac:dyDescent="0.55000000000000004">
       <c r="B157" s="1" t="s">
-        <v>298</v>
+        <v>270</v>
       </c>
       <c r="C157" s="1" t="s">
         <v>242</v>
@@ -4379,13 +4381,13 @@
         <v>62</v>
       </c>
       <c r="E157" s="1" t="s">
-        <v>299</v>
+        <v>271</v>
       </c>
       <c r="G157" s="1"/>
     </row>
     <row r="158" spans="2:7" x14ac:dyDescent="0.55000000000000004">
       <c r="B158" s="1" t="s">
-        <v>300</v>
+        <v>272</v>
       </c>
       <c r="C158" s="1" t="s">
         <v>242</v>
@@ -4394,13 +4396,13 @@
         <v>62</v>
       </c>
       <c r="E158" s="1" t="s">
-        <v>301</v>
+        <v>273</v>
       </c>
       <c r="G158" s="1"/>
     </row>
     <row r="159" spans="2:7" x14ac:dyDescent="0.55000000000000004">
       <c r="B159" s="1" t="s">
-        <v>302</v>
+        <v>274</v>
       </c>
       <c r="C159" s="1" t="s">
         <v>242</v>
@@ -4409,13 +4411,13 @@
         <v>62</v>
       </c>
       <c r="E159" s="1" t="s">
-        <v>303</v>
+        <v>275</v>
       </c>
       <c r="G159" s="1"/>
     </row>
     <row r="160" spans="2:7" x14ac:dyDescent="0.55000000000000004">
       <c r="B160" s="1" t="s">
-        <v>304</v>
+        <v>276</v>
       </c>
       <c r="C160" s="1" t="s">
         <v>242</v>
@@ -4424,13 +4426,13 @@
         <v>62</v>
       </c>
       <c r="E160" s="1" t="s">
-        <v>305</v>
+        <v>277</v>
       </c>
       <c r="G160" s="1"/>
     </row>
     <row r="161" spans="2:7" x14ac:dyDescent="0.55000000000000004">
       <c r="B161" s="1" t="s">
-        <v>306</v>
+        <v>278</v>
       </c>
       <c r="C161" s="1" t="s">
         <v>242</v>
@@ -4439,13 +4441,13 @@
         <v>62</v>
       </c>
       <c r="E161" s="1" t="s">
-        <v>307</v>
+        <v>279</v>
       </c>
       <c r="G161" s="1"/>
     </row>
     <row r="162" spans="2:7" x14ac:dyDescent="0.55000000000000004">
       <c r="B162" s="1" t="s">
-        <v>308</v>
+        <v>280</v>
       </c>
       <c r="C162" s="1" t="s">
         <v>242</v>
@@ -4454,13 +4456,13 @@
         <v>62</v>
       </c>
       <c r="E162" s="1" t="s">
-        <v>309</v>
+        <v>95</v>
       </c>
       <c r="G162" s="1"/>
     </row>
     <row r="163" spans="2:7" x14ac:dyDescent="0.55000000000000004">
       <c r="B163" s="1" t="s">
-        <v>310</v>
+        <v>281</v>
       </c>
       <c r="C163" s="1" t="s">
         <v>242</v>
@@ -4469,13 +4471,13 @@
         <v>62</v>
       </c>
       <c r="E163" s="1" t="s">
-        <v>311</v>
+        <v>97</v>
       </c>
       <c r="G163" s="1"/>
     </row>
     <row r="164" spans="2:7" x14ac:dyDescent="0.55000000000000004">
       <c r="B164" s="1" t="s">
-        <v>312</v>
+        <v>282</v>
       </c>
       <c r="C164" s="1" t="s">
         <v>242</v>
@@ -4484,13 +4486,13 @@
         <v>62</v>
       </c>
       <c r="E164" s="1" t="s">
-        <v>313</v>
+        <v>99</v>
       </c>
       <c r="G164" s="1"/>
     </row>
     <row r="165" spans="2:7" x14ac:dyDescent="0.55000000000000004">
       <c r="B165" s="1" t="s">
-        <v>314</v>
+        <v>283</v>
       </c>
       <c r="C165" s="1" t="s">
         <v>242</v>
@@ -4499,13 +4501,13 @@
         <v>62</v>
       </c>
       <c r="E165" s="1" t="s">
-        <v>315</v>
+        <v>101</v>
       </c>
       <c r="G165" s="1"/>
     </row>
     <row r="166" spans="2:7" x14ac:dyDescent="0.55000000000000004">
       <c r="B166" s="1" t="s">
-        <v>316</v>
+        <v>284</v>
       </c>
       <c r="C166" s="1" t="s">
         <v>242</v>
@@ -4514,13 +4516,13 @@
         <v>62</v>
       </c>
       <c r="E166" s="1" t="s">
-        <v>317</v>
+        <v>103</v>
       </c>
       <c r="G166" s="1"/>
     </row>
     <row r="167" spans="2:7" x14ac:dyDescent="0.55000000000000004">
       <c r="B167" s="1" t="s">
-        <v>318</v>
+        <v>285</v>
       </c>
       <c r="C167" s="1" t="s">
         <v>242</v>
@@ -4529,13 +4531,13 @@
         <v>62</v>
       </c>
       <c r="E167" s="1" t="s">
-        <v>319</v>
+        <v>286</v>
       </c>
       <c r="G167" s="1"/>
     </row>
     <row r="168" spans="2:7" x14ac:dyDescent="0.55000000000000004">
       <c r="B168" s="1" t="s">
-        <v>320</v>
+        <v>287</v>
       </c>
       <c r="C168" s="1" t="s">
         <v>242</v>
@@ -4544,13 +4546,13 @@
         <v>62</v>
       </c>
       <c r="E168" s="1" t="s">
-        <v>321</v>
+        <v>288</v>
       </c>
       <c r="G168" s="1"/>
     </row>
     <row r="169" spans="2:7" x14ac:dyDescent="0.55000000000000004">
       <c r="B169" s="1" t="s">
-        <v>322</v>
+        <v>289</v>
       </c>
       <c r="C169" s="1" t="s">
         <v>242</v>
@@ -4559,13 +4561,13 @@
         <v>62</v>
       </c>
       <c r="E169" s="1" t="s">
-        <v>323</v>
+        <v>290</v>
       </c>
       <c r="G169" s="1"/>
     </row>
     <row r="170" spans="2:7" x14ac:dyDescent="0.55000000000000004">
       <c r="B170" s="1" t="s">
-        <v>324</v>
+        <v>291</v>
       </c>
       <c r="C170" s="1" t="s">
         <v>242</v>
@@ -4574,13 +4576,13 @@
         <v>62</v>
       </c>
       <c r="E170" s="1" t="s">
-        <v>325</v>
+        <v>292</v>
       </c>
       <c r="G170" s="1"/>
     </row>
     <row r="171" spans="2:7" x14ac:dyDescent="0.55000000000000004">
       <c r="B171" s="1" t="s">
-        <v>326</v>
+        <v>293</v>
       </c>
       <c r="C171" s="1" t="s">
         <v>242</v>
@@ -4589,13 +4591,13 @@
         <v>62</v>
       </c>
       <c r="E171" s="1" t="s">
-        <v>327</v>
+        <v>294</v>
       </c>
       <c r="G171" s="1"/>
     </row>
     <row r="172" spans="2:7" x14ac:dyDescent="0.55000000000000004">
       <c r="B172" s="1" t="s">
-        <v>328</v>
+        <v>295</v>
       </c>
       <c r="C172" s="1" t="s">
         <v>242</v>
@@ -4604,13 +4606,13 @@
         <v>62</v>
       </c>
       <c r="E172" s="1" t="s">
-        <v>329</v>
+        <v>296</v>
       </c>
       <c r="G172" s="1"/>
     </row>
     <row r="173" spans="2:7" x14ac:dyDescent="0.55000000000000004">
       <c r="B173" s="1" t="s">
-        <v>330</v>
+        <v>297</v>
       </c>
       <c r="C173" s="1" t="s">
         <v>242</v>
@@ -4619,13 +4621,13 @@
         <v>62</v>
       </c>
       <c r="E173" s="1" t="s">
-        <v>331</v>
+        <v>229</v>
       </c>
       <c r="G173" s="1"/>
     </row>
     <row r="174" spans="2:7" x14ac:dyDescent="0.55000000000000004">
       <c r="B174" s="1" t="s">
-        <v>332</v>
+        <v>298</v>
       </c>
       <c r="C174" s="1" t="s">
         <v>242</v>
@@ -4634,13 +4636,13 @@
         <v>62</v>
       </c>
       <c r="E174" s="1" t="s">
-        <v>333</v>
+        <v>299</v>
       </c>
       <c r="G174" s="1"/>
     </row>
     <row r="175" spans="2:7" x14ac:dyDescent="0.55000000000000004">
       <c r="B175" s="1" t="s">
-        <v>334</v>
+        <v>300</v>
       </c>
       <c r="C175" s="1" t="s">
         <v>242</v>
@@ -4649,13 +4651,13 @@
         <v>62</v>
       </c>
       <c r="E175" s="1" t="s">
-        <v>335</v>
+        <v>301</v>
       </c>
       <c r="G175" s="1"/>
     </row>
     <row r="176" spans="2:7" x14ac:dyDescent="0.55000000000000004">
       <c r="B176" s="1" t="s">
-        <v>336</v>
+        <v>302</v>
       </c>
       <c r="C176" s="1" t="s">
         <v>242</v>
@@ -4664,13 +4666,13 @@
         <v>62</v>
       </c>
       <c r="E176" s="1" t="s">
-        <v>337</v>
+        <v>303</v>
       </c>
       <c r="G176" s="1"/>
     </row>
     <row r="177" spans="2:7" x14ac:dyDescent="0.55000000000000004">
       <c r="B177" s="1" t="s">
-        <v>338</v>
+        <v>304</v>
       </c>
       <c r="C177" s="1" t="s">
         <v>242</v>
@@ -4679,13 +4681,13 @@
         <v>62</v>
       </c>
       <c r="E177" s="1" t="s">
-        <v>339</v>
+        <v>305</v>
       </c>
       <c r="G177" s="1"/>
     </row>
     <row r="178" spans="2:7" x14ac:dyDescent="0.55000000000000004">
       <c r="B178" s="1" t="s">
-        <v>340</v>
+        <v>306</v>
       </c>
       <c r="C178" s="1" t="s">
         <v>242</v>
@@ -4694,13 +4696,13 @@
         <v>62</v>
       </c>
       <c r="E178" s="1" t="s">
-        <v>341</v>
+        <v>307</v>
       </c>
       <c r="G178" s="1"/>
     </row>
     <row r="179" spans="2:7" x14ac:dyDescent="0.55000000000000004">
       <c r="B179" s="1" t="s">
-        <v>342</v>
+        <v>308</v>
       </c>
       <c r="C179" s="1" t="s">
         <v>242</v>
@@ -4709,13 +4711,13 @@
         <v>62</v>
       </c>
       <c r="E179" s="1" t="s">
-        <v>343</v>
+        <v>309</v>
       </c>
       <c r="G179" s="1"/>
     </row>
     <row r="180" spans="2:7" x14ac:dyDescent="0.55000000000000004">
       <c r="B180" s="1" t="s">
-        <v>344</v>
+        <v>310</v>
       </c>
       <c r="C180" s="1" t="s">
         <v>242</v>
@@ -4724,13 +4726,13 @@
         <v>62</v>
       </c>
       <c r="E180" s="1" t="s">
-        <v>345</v>
+        <v>311</v>
       </c>
       <c r="G180" s="1"/>
     </row>
     <row r="181" spans="2:7" x14ac:dyDescent="0.55000000000000004">
       <c r="B181" s="1" t="s">
-        <v>346</v>
+        <v>312</v>
       </c>
       <c r="C181" s="1" t="s">
         <v>242</v>
@@ -4739,13 +4741,13 @@
         <v>62</v>
       </c>
       <c r="E181" s="1" t="s">
-        <v>347</v>
+        <v>313</v>
       </c>
       <c r="G181" s="1"/>
     </row>
     <row r="182" spans="2:7" x14ac:dyDescent="0.55000000000000004">
       <c r="B182" s="1" t="s">
-        <v>348</v>
+        <v>314</v>
       </c>
       <c r="C182" s="1" t="s">
         <v>242</v>
@@ -4754,13 +4756,13 @@
         <v>62</v>
       </c>
       <c r="E182" s="1" t="s">
-        <v>349</v>
+        <v>315</v>
       </c>
       <c r="G182" s="1"/>
     </row>
     <row r="183" spans="2:7" x14ac:dyDescent="0.55000000000000004">
       <c r="B183" s="1" t="s">
-        <v>350</v>
+        <v>316</v>
       </c>
       <c r="C183" s="1" t="s">
         <v>242</v>
@@ -4769,13 +4771,13 @@
         <v>62</v>
       </c>
       <c r="E183" s="1" t="s">
-        <v>351</v>
+        <v>317</v>
       </c>
       <c r="G183" s="1"/>
     </row>
     <row r="184" spans="2:7" x14ac:dyDescent="0.55000000000000004">
       <c r="B184" s="1" t="s">
-        <v>352</v>
+        <v>318</v>
       </c>
       <c r="C184" s="1" t="s">
         <v>242</v>
@@ -4784,13 +4786,13 @@
         <v>62</v>
       </c>
       <c r="E184" s="1" t="s">
-        <v>353</v>
+        <v>319</v>
       </c>
       <c r="G184" s="1"/>
     </row>
     <row r="185" spans="2:7" x14ac:dyDescent="0.55000000000000004">
       <c r="B185" s="1" t="s">
-        <v>354</v>
+        <v>320</v>
       </c>
       <c r="C185" s="1" t="s">
         <v>242</v>
@@ -4799,13 +4801,13 @@
         <v>62</v>
       </c>
       <c r="E185" s="1" t="s">
-        <v>355</v>
+        <v>321</v>
       </c>
       <c r="G185" s="1"/>
     </row>
     <row r="186" spans="2:7" x14ac:dyDescent="0.55000000000000004">
       <c r="B186" s="1" t="s">
-        <v>356</v>
+        <v>322</v>
       </c>
       <c r="C186" s="1" t="s">
         <v>242</v>
@@ -4814,13 +4816,13 @@
         <v>62</v>
       </c>
       <c r="E186" s="1" t="s">
-        <v>357</v>
+        <v>323</v>
       </c>
       <c r="G186" s="1"/>
     </row>
     <row r="187" spans="2:7" x14ac:dyDescent="0.55000000000000004">
       <c r="B187" s="1" t="s">
-        <v>358</v>
+        <v>324</v>
       </c>
       <c r="C187" s="1" t="s">
         <v>242</v>
@@ -4829,13 +4831,13 @@
         <v>62</v>
       </c>
       <c r="E187" s="1" t="s">
-        <v>359</v>
+        <v>325</v>
       </c>
       <c r="G187" s="1"/>
     </row>
     <row r="188" spans="2:7" x14ac:dyDescent="0.55000000000000004">
       <c r="B188" s="1" t="s">
-        <v>360</v>
+        <v>326</v>
       </c>
       <c r="C188" s="1" t="s">
         <v>242</v>
@@ -4844,13 +4846,13 @@
         <v>62</v>
       </c>
       <c r="E188" s="1" t="s">
-        <v>361</v>
+        <v>327</v>
       </c>
       <c r="G188" s="1"/>
     </row>
     <row r="189" spans="2:7" x14ac:dyDescent="0.55000000000000004">
       <c r="B189" s="1" t="s">
-        <v>362</v>
+        <v>328</v>
       </c>
       <c r="C189" s="1" t="s">
         <v>242</v>
@@ -4859,13 +4861,13 @@
         <v>62</v>
       </c>
       <c r="E189" s="1" t="s">
-        <v>363</v>
+        <v>329</v>
       </c>
       <c r="G189" s="1"/>
     </row>
     <row r="190" spans="2:7" x14ac:dyDescent="0.55000000000000004">
       <c r="B190" s="1" t="s">
-        <v>364</v>
+        <v>330</v>
       </c>
       <c r="C190" s="1" t="s">
         <v>242</v>
@@ -4874,13 +4876,13 @@
         <v>62</v>
       </c>
       <c r="E190" s="1" t="s">
-        <v>365</v>
+        <v>331</v>
       </c>
       <c r="G190" s="1"/>
     </row>
     <row r="191" spans="2:7" x14ac:dyDescent="0.55000000000000004">
       <c r="B191" s="1" t="s">
-        <v>366</v>
+        <v>332</v>
       </c>
       <c r="C191" s="1" t="s">
         <v>242</v>
@@ -4889,13 +4891,13 @@
         <v>62</v>
       </c>
       <c r="E191" s="1" t="s">
-        <v>367</v>
+        <v>333</v>
       </c>
       <c r="G191" s="1"/>
     </row>
     <row r="192" spans="2:7" x14ac:dyDescent="0.55000000000000004">
       <c r="B192" s="1" t="s">
-        <v>368</v>
+        <v>334</v>
       </c>
       <c r="C192" s="1" t="s">
         <v>242</v>
@@ -4904,13 +4906,13 @@
         <v>62</v>
       </c>
       <c r="E192" s="1" t="s">
-        <v>369</v>
+        <v>335</v>
       </c>
       <c r="G192" s="1"/>
     </row>
     <row r="193" spans="2:7" x14ac:dyDescent="0.55000000000000004">
       <c r="B193" s="1" t="s">
-        <v>370</v>
+        <v>336</v>
       </c>
       <c r="C193" s="1" t="s">
         <v>242</v>
@@ -4919,13 +4921,13 @@
         <v>62</v>
       </c>
       <c r="E193" s="1" t="s">
-        <v>371</v>
+        <v>337</v>
       </c>
       <c r="G193" s="1"/>
     </row>
     <row r="194" spans="2:7" x14ac:dyDescent="0.55000000000000004">
       <c r="B194" s="1" t="s">
-        <v>372</v>
+        <v>338</v>
       </c>
       <c r="C194" s="1" t="s">
         <v>242</v>
@@ -4934,13 +4936,13 @@
         <v>62</v>
       </c>
       <c r="E194" s="1" t="s">
-        <v>373</v>
+        <v>339</v>
       </c>
       <c r="G194" s="1"/>
     </row>
     <row r="195" spans="2:7" x14ac:dyDescent="0.55000000000000004">
       <c r="B195" s="1" t="s">
-        <v>374</v>
+        <v>340</v>
       </c>
       <c r="C195" s="1" t="s">
         <v>242</v>
@@ -4949,13 +4951,13 @@
         <v>62</v>
       </c>
       <c r="E195" s="1" t="s">
-        <v>375</v>
+        <v>341</v>
       </c>
       <c r="G195" s="1"/>
     </row>
     <row r="196" spans="2:7" x14ac:dyDescent="0.55000000000000004">
       <c r="B196" s="1" t="s">
-        <v>376</v>
+        <v>342</v>
       </c>
       <c r="C196" s="1" t="s">
         <v>242</v>
@@ -4964,13 +4966,13 @@
         <v>62</v>
       </c>
       <c r="E196" s="1" t="s">
-        <v>377</v>
+        <v>343</v>
       </c>
       <c r="G196" s="1"/>
     </row>
     <row r="197" spans="2:7" x14ac:dyDescent="0.55000000000000004">
       <c r="B197" s="1" t="s">
-        <v>378</v>
+        <v>344</v>
       </c>
       <c r="C197" s="1" t="s">
         <v>242</v>
@@ -4979,13 +4981,13 @@
         <v>62</v>
       </c>
       <c r="E197" s="1" t="s">
-        <v>379</v>
+        <v>345</v>
       </c>
       <c r="G197" s="1"/>
     </row>
     <row r="198" spans="2:7" x14ac:dyDescent="0.55000000000000004">
       <c r="B198" s="1" t="s">
-        <v>380</v>
+        <v>346</v>
       </c>
       <c r="C198" s="1" t="s">
         <v>242</v>
@@ -4994,13 +4996,13 @@
         <v>62</v>
       </c>
       <c r="E198" s="1" t="s">
-        <v>381</v>
+        <v>347</v>
       </c>
       <c r="G198" s="1"/>
     </row>
     <row r="199" spans="2:7" x14ac:dyDescent="0.55000000000000004">
       <c r="B199" s="1" t="s">
-        <v>382</v>
+        <v>348</v>
       </c>
       <c r="C199" s="1" t="s">
         <v>242</v>
@@ -5009,13 +5011,13 @@
         <v>62</v>
       </c>
       <c r="E199" s="1" t="s">
-        <v>383</v>
+        <v>349</v>
       </c>
       <c r="G199" s="1"/>
     </row>
     <row r="200" spans="2:7" x14ac:dyDescent="0.55000000000000004">
       <c r="B200" s="1" t="s">
-        <v>384</v>
+        <v>350</v>
       </c>
       <c r="C200" s="1" t="s">
         <v>242</v>
@@ -5024,13 +5026,13 @@
         <v>62</v>
       </c>
       <c r="E200" s="1" t="s">
-        <v>385</v>
+        <v>351</v>
       </c>
       <c r="G200" s="1"/>
     </row>
     <row r="201" spans="2:7" x14ac:dyDescent="0.55000000000000004">
       <c r="B201" s="1" t="s">
-        <v>386</v>
+        <v>352</v>
       </c>
       <c r="C201" s="1" t="s">
         <v>242</v>
@@ -5039,13 +5041,13 @@
         <v>62</v>
       </c>
       <c r="E201" s="1" t="s">
-        <v>387</v>
+        <v>353</v>
       </c>
       <c r="G201" s="1"/>
     </row>
     <row r="202" spans="2:7" x14ac:dyDescent="0.55000000000000004">
       <c r="B202" s="1" t="s">
-        <v>388</v>
+        <v>354</v>
       </c>
       <c r="C202" s="1" t="s">
         <v>242</v>
@@ -5054,13 +5056,13 @@
         <v>62</v>
       </c>
       <c r="E202" s="1" t="s">
-        <v>389</v>
+        <v>355</v>
       </c>
       <c r="G202" s="1"/>
     </row>
     <row r="203" spans="2:7" x14ac:dyDescent="0.55000000000000004">
       <c r="B203" s="1" t="s">
-        <v>390</v>
+        <v>356</v>
       </c>
       <c r="C203" s="1" t="s">
         <v>242</v>
@@ -5069,13 +5071,13 @@
         <v>62</v>
       </c>
       <c r="E203" s="1" t="s">
-        <v>391</v>
+        <v>357</v>
       </c>
       <c r="G203" s="1"/>
     </row>
     <row r="204" spans="2:7" x14ac:dyDescent="0.55000000000000004">
       <c r="B204" s="1" t="s">
-        <v>392</v>
+        <v>358</v>
       </c>
       <c r="C204" s="1" t="s">
         <v>242</v>
@@ -5084,13 +5086,13 @@
         <v>62</v>
       </c>
       <c r="E204" s="1" t="s">
-        <v>393</v>
+        <v>359</v>
       </c>
       <c r="G204" s="1"/>
     </row>
     <row r="205" spans="2:7" x14ac:dyDescent="0.55000000000000004">
       <c r="B205" s="1" t="s">
-        <v>394</v>
+        <v>360</v>
       </c>
       <c r="C205" s="1" t="s">
         <v>242</v>
@@ -5099,13 +5101,13 @@
         <v>62</v>
       </c>
       <c r="E205" s="1" t="s">
-        <v>395</v>
+        <v>361</v>
       </c>
       <c r="G205" s="1"/>
     </row>
     <row r="206" spans="2:7" x14ac:dyDescent="0.55000000000000004">
       <c r="B206" s="1" t="s">
-        <v>396</v>
+        <v>362</v>
       </c>
       <c r="C206" s="1" t="s">
         <v>242</v>
@@ -5114,13 +5116,13 @@
         <v>62</v>
       </c>
       <c r="E206" s="1" t="s">
-        <v>397</v>
+        <v>363</v>
       </c>
       <c r="G206" s="1"/>
     </row>
     <row r="207" spans="2:7" x14ac:dyDescent="0.55000000000000004">
       <c r="B207" s="1" t="s">
-        <v>398</v>
+        <v>364</v>
       </c>
       <c r="C207" s="1" t="s">
         <v>242</v>
@@ -5129,13 +5131,13 @@
         <v>62</v>
       </c>
       <c r="E207" s="1" t="s">
-        <v>399</v>
+        <v>365</v>
       </c>
       <c r="G207" s="1"/>
     </row>
     <row r="208" spans="2:7" x14ac:dyDescent="0.55000000000000004">
       <c r="B208" s="1" t="s">
-        <v>400</v>
+        <v>366</v>
       </c>
       <c r="C208" s="1" t="s">
         <v>242</v>
@@ -5144,13 +5146,13 @@
         <v>62</v>
       </c>
       <c r="E208" s="1" t="s">
-        <v>401</v>
+        <v>367</v>
       </c>
       <c r="G208" s="1"/>
     </row>
     <row r="209" spans="2:7" x14ac:dyDescent="0.55000000000000004">
       <c r="B209" s="1" t="s">
-        <v>402</v>
+        <v>368</v>
       </c>
       <c r="C209" s="1" t="s">
         <v>242</v>
@@ -5159,13 +5161,13 @@
         <v>62</v>
       </c>
       <c r="E209" s="1" t="s">
-        <v>403</v>
+        <v>369</v>
       </c>
       <c r="G209" s="1"/>
     </row>
     <row r="210" spans="2:7" x14ac:dyDescent="0.55000000000000004">
       <c r="B210" s="1" t="s">
-        <v>404</v>
+        <v>370</v>
       </c>
       <c r="C210" s="1" t="s">
         <v>242</v>
@@ -5174,13 +5176,13 @@
         <v>62</v>
       </c>
       <c r="E210" s="1" t="s">
-        <v>405</v>
+        <v>371</v>
       </c>
       <c r="G210" s="1"/>
     </row>
     <row r="211" spans="2:7" x14ac:dyDescent="0.55000000000000004">
       <c r="B211" s="1" t="s">
-        <v>406</v>
+        <v>372</v>
       </c>
       <c r="C211" s="1" t="s">
         <v>242</v>
@@ -5189,13 +5191,13 @@
         <v>62</v>
       </c>
       <c r="E211" s="1" t="s">
-        <v>407</v>
+        <v>373</v>
       </c>
       <c r="G211" s="1"/>
     </row>
     <row r="212" spans="2:7" x14ac:dyDescent="0.55000000000000004">
       <c r="B212" s="1" t="s">
-        <v>408</v>
+        <v>374</v>
       </c>
       <c r="C212" s="1" t="s">
         <v>242</v>
@@ -5204,13 +5206,13 @@
         <v>62</v>
       </c>
       <c r="E212" s="1" t="s">
-        <v>409</v>
+        <v>375</v>
       </c>
       <c r="G212" s="1"/>
     </row>
     <row r="213" spans="2:7" x14ac:dyDescent="0.55000000000000004">
       <c r="B213" s="1" t="s">
-        <v>410</v>
+        <v>376</v>
       </c>
       <c r="C213" s="1" t="s">
         <v>242</v>
@@ -5219,13 +5221,13 @@
         <v>62</v>
       </c>
       <c r="E213" s="1" t="s">
-        <v>411</v>
+        <v>377</v>
       </c>
       <c r="G213" s="1"/>
     </row>
     <row r="214" spans="2:7" x14ac:dyDescent="0.55000000000000004">
       <c r="B214" s="1" t="s">
-        <v>412</v>
+        <v>378</v>
       </c>
       <c r="C214" s="1" t="s">
         <v>242</v>
@@ -5234,13 +5236,13 @@
         <v>62</v>
       </c>
       <c r="E214" s="1" t="s">
-        <v>413</v>
+        <v>379</v>
       </c>
       <c r="G214" s="1"/>
     </row>
     <row r="215" spans="2:7" x14ac:dyDescent="0.55000000000000004">
       <c r="B215" s="1" t="s">
-        <v>414</v>
+        <v>380</v>
       </c>
       <c r="C215" s="1" t="s">
         <v>242</v>
@@ -5249,13 +5251,13 @@
         <v>62</v>
       </c>
       <c r="E215" s="1" t="s">
-        <v>415</v>
+        <v>381</v>
       </c>
       <c r="G215" s="1"/>
     </row>
     <row r="216" spans="2:7" x14ac:dyDescent="0.55000000000000004">
       <c r="B216" s="1" t="s">
-        <v>416</v>
+        <v>382</v>
       </c>
       <c r="C216" s="1" t="s">
         <v>242</v>
@@ -5264,13 +5266,13 @@
         <v>62</v>
       </c>
       <c r="E216" s="1" t="s">
-        <v>417</v>
+        <v>383</v>
       </c>
       <c r="G216" s="1"/>
     </row>
     <row r="217" spans="2:7" x14ac:dyDescent="0.55000000000000004">
       <c r="B217" s="1" t="s">
-        <v>418</v>
+        <v>384</v>
       </c>
       <c r="C217" s="1" t="s">
         <v>242</v>
@@ -5279,13 +5281,13 @@
         <v>62</v>
       </c>
       <c r="E217" s="1" t="s">
-        <v>419</v>
+        <v>385</v>
       </c>
       <c r="G217" s="1"/>
     </row>
     <row r="218" spans="2:7" x14ac:dyDescent="0.55000000000000004">
       <c r="B218" s="1" t="s">
-        <v>420</v>
+        <v>386</v>
       </c>
       <c r="C218" s="1" t="s">
         <v>242</v>
@@ -5294,13 +5296,13 @@
         <v>62</v>
       </c>
       <c r="E218" s="1" t="s">
-        <v>421</v>
+        <v>387</v>
       </c>
       <c r="G218" s="1"/>
     </row>
     <row r="219" spans="2:7" x14ac:dyDescent="0.55000000000000004">
       <c r="B219" s="1" t="s">
-        <v>422</v>
+        <v>388</v>
       </c>
       <c r="C219" s="1" t="s">
         <v>242</v>
@@ -5309,13 +5311,13 @@
         <v>62</v>
       </c>
       <c r="E219" s="1" t="s">
-        <v>423</v>
+        <v>389</v>
       </c>
       <c r="G219" s="1"/>
     </row>
     <row r="220" spans="2:7" x14ac:dyDescent="0.55000000000000004">
       <c r="B220" s="1" t="s">
-        <v>424</v>
+        <v>390</v>
       </c>
       <c r="C220" s="1" t="s">
         <v>242</v>
@@ -5324,13 +5326,13 @@
         <v>62</v>
       </c>
       <c r="E220" s="1" t="s">
-        <v>425</v>
+        <v>391</v>
       </c>
       <c r="G220" s="1"/>
     </row>
     <row r="221" spans="2:7" x14ac:dyDescent="0.55000000000000004">
       <c r="B221" s="1" t="s">
-        <v>426</v>
+        <v>392</v>
       </c>
       <c r="C221" s="1" t="s">
         <v>242</v>
@@ -5339,13 +5341,13 @@
         <v>62</v>
       </c>
       <c r="E221" s="1" t="s">
-        <v>425</v>
+        <v>393</v>
       </c>
       <c r="G221" s="1"/>
     </row>
     <row r="222" spans="2:7" x14ac:dyDescent="0.55000000000000004">
       <c r="B222" s="1" t="s">
-        <v>427</v>
+        <v>394</v>
       </c>
       <c r="C222" s="1" t="s">
         <v>242</v>
@@ -5354,13 +5356,13 @@
         <v>62</v>
       </c>
       <c r="E222" s="1" t="s">
-        <v>425</v>
+        <v>395</v>
       </c>
       <c r="G222" s="1"/>
     </row>
     <row r="223" spans="2:7" x14ac:dyDescent="0.55000000000000004">
       <c r="B223" s="1" t="s">
-        <v>428</v>
+        <v>396</v>
       </c>
       <c r="C223" s="1" t="s">
         <v>242</v>
@@ -5369,13 +5371,13 @@
         <v>62</v>
       </c>
       <c r="E223" s="1" t="s">
-        <v>425</v>
+        <v>397</v>
       </c>
       <c r="G223" s="1"/>
     </row>
     <row r="224" spans="2:7" x14ac:dyDescent="0.55000000000000004">
       <c r="B224" s="1" t="s">
-        <v>429</v>
+        <v>398</v>
       </c>
       <c r="C224" s="1" t="s">
         <v>242</v>
@@ -5384,13 +5386,13 @@
         <v>62</v>
       </c>
       <c r="E224" s="1" t="s">
-        <v>425</v>
+        <v>399</v>
       </c>
       <c r="G224" s="1"/>
     </row>
     <row r="225" spans="2:7" x14ac:dyDescent="0.55000000000000004">
       <c r="B225" s="1" t="s">
-        <v>430</v>
+        <v>400</v>
       </c>
       <c r="C225" s="1" t="s">
         <v>242</v>
@@ -5399,13 +5401,13 @@
         <v>62</v>
       </c>
       <c r="E225" s="1" t="s">
-        <v>425</v>
+        <v>401</v>
       </c>
       <c r="G225" s="1"/>
     </row>
     <row r="226" spans="2:7" x14ac:dyDescent="0.55000000000000004">
       <c r="B226" s="1" t="s">
-        <v>431</v>
+        <v>402</v>
       </c>
       <c r="C226" s="1" t="s">
         <v>242</v>
@@ -5414,13 +5416,13 @@
         <v>62</v>
       </c>
       <c r="E226" s="1" t="s">
-        <v>425</v>
+        <v>403</v>
       </c>
       <c r="G226" s="1"/>
     </row>
     <row r="227" spans="2:7" x14ac:dyDescent="0.55000000000000004">
       <c r="B227" s="1" t="s">
-        <v>432</v>
+        <v>404</v>
       </c>
       <c r="C227" s="1" t="s">
         <v>242</v>
@@ -5429,13 +5431,13 @@
         <v>62</v>
       </c>
       <c r="E227" s="1" t="s">
-        <v>425</v>
+        <v>405</v>
       </c>
       <c r="G227" s="1"/>
     </row>
     <row r="228" spans="2:7" x14ac:dyDescent="0.55000000000000004">
       <c r="B228" s="1" t="s">
-        <v>433</v>
+        <v>406</v>
       </c>
       <c r="C228" s="1" t="s">
         <v>242</v>
@@ -5444,13 +5446,13 @@
         <v>62</v>
       </c>
       <c r="E228" s="1" t="s">
-        <v>425</v>
+        <v>407</v>
       </c>
       <c r="G228" s="1"/>
     </row>
     <row r="229" spans="2:7" x14ac:dyDescent="0.55000000000000004">
       <c r="B229" s="1" t="s">
-        <v>434</v>
+        <v>408</v>
       </c>
       <c r="C229" s="1" t="s">
         <v>242</v>
@@ -5459,13 +5461,13 @@
         <v>62</v>
       </c>
       <c r="E229" s="1" t="s">
-        <v>425</v>
+        <v>409</v>
       </c>
       <c r="G229" s="1"/>
     </row>
     <row r="230" spans="2:7" x14ac:dyDescent="0.55000000000000004">
       <c r="B230" s="1" t="s">
-        <v>435</v>
+        <v>410</v>
       </c>
       <c r="C230" s="1" t="s">
         <v>242</v>
@@ -5474,13 +5476,13 @@
         <v>62</v>
       </c>
       <c r="E230" s="1" t="s">
-        <v>425</v>
+        <v>411</v>
       </c>
       <c r="G230" s="1"/>
     </row>
     <row r="231" spans="2:7" x14ac:dyDescent="0.55000000000000004">
       <c r="B231" s="1" t="s">
-        <v>436</v>
+        <v>412</v>
       </c>
       <c r="C231" s="1" t="s">
         <v>242</v>
@@ -5489,13 +5491,13 @@
         <v>62</v>
       </c>
       <c r="E231" s="1" t="s">
-        <v>425</v>
+        <v>413</v>
       </c>
       <c r="G231" s="1"/>
     </row>
     <row r="232" spans="2:7" x14ac:dyDescent="0.55000000000000004">
       <c r="B232" s="1" t="s">
-        <v>437</v>
+        <v>414</v>
       </c>
       <c r="C232" s="1" t="s">
         <v>242</v>
@@ -5504,13 +5506,13 @@
         <v>62</v>
       </c>
       <c r="E232" s="1" t="s">
-        <v>425</v>
+        <v>415</v>
       </c>
       <c r="G232" s="1"/>
     </row>
     <row r="233" spans="2:7" x14ac:dyDescent="0.55000000000000004">
       <c r="B233" s="1" t="s">
-        <v>438</v>
+        <v>416</v>
       </c>
       <c r="C233" s="1" t="s">
         <v>242</v>
@@ -5519,24 +5521,279 @@
         <v>62</v>
       </c>
       <c r="E233" s="1" t="s">
-        <v>425</v>
+        <v>417</v>
       </c>
       <c r="G233" s="1"/>
     </row>
     <row r="234" spans="2:7" x14ac:dyDescent="0.55000000000000004">
       <c r="B234" s="1" t="s">
+        <v>418</v>
+      </c>
+      <c r="C234" s="1" t="s">
+        <v>242</v>
+      </c>
+      <c r="D234" t="s">
+        <v>62</v>
+      </c>
+      <c r="E234" s="1" t="s">
+        <v>419</v>
+      </c>
+      <c r="G234" s="1"/>
+    </row>
+    <row r="235" spans="2:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="B235" s="1" t="s">
+        <v>420</v>
+      </c>
+      <c r="C235" s="1" t="s">
+        <v>242</v>
+      </c>
+      <c r="D235" t="s">
+        <v>62</v>
+      </c>
+      <c r="E235" s="1" t="s">
+        <v>421</v>
+      </c>
+      <c r="G235" s="1"/>
+    </row>
+    <row r="236" spans="2:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="B236" s="1" t="s">
+        <v>422</v>
+      </c>
+      <c r="C236" s="1" t="s">
+        <v>242</v>
+      </c>
+      <c r="D236" t="s">
+        <v>62</v>
+      </c>
+      <c r="E236" s="1" t="s">
+        <v>423</v>
+      </c>
+      <c r="G236" s="1"/>
+    </row>
+    <row r="237" spans="2:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="B237" s="1" t="s">
+        <v>424</v>
+      </c>
+      <c r="C237" s="1" t="s">
+        <v>242</v>
+      </c>
+      <c r="D237" t="s">
+        <v>62</v>
+      </c>
+      <c r="E237" s="1" t="s">
+        <v>425</v>
+      </c>
+      <c r="G237" s="1"/>
+    </row>
+    <row r="238" spans="2:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="B238" s="1" t="s">
+        <v>426</v>
+      </c>
+      <c r="C238" s="1" t="s">
+        <v>242</v>
+      </c>
+      <c r="D238" t="s">
+        <v>62</v>
+      </c>
+      <c r="E238" s="1" t="s">
+        <v>425</v>
+      </c>
+      <c r="G238" s="1"/>
+    </row>
+    <row r="239" spans="2:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="B239" s="1" t="s">
+        <v>427</v>
+      </c>
+      <c r="C239" s="1" t="s">
+        <v>242</v>
+      </c>
+      <c r="D239" t="s">
+        <v>62</v>
+      </c>
+      <c r="E239" s="1" t="s">
+        <v>425</v>
+      </c>
+      <c r="G239" s="1"/>
+    </row>
+    <row r="240" spans="2:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="B240" s="1" t="s">
+        <v>428</v>
+      </c>
+      <c r="C240" s="1" t="s">
+        <v>242</v>
+      </c>
+      <c r="D240" t="s">
+        <v>62</v>
+      </c>
+      <c r="E240" s="1" t="s">
+        <v>425</v>
+      </c>
+      <c r="G240" s="1"/>
+    </row>
+    <row r="241" spans="2:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="B241" s="1" t="s">
+        <v>429</v>
+      </c>
+      <c r="C241" s="1" t="s">
+        <v>242</v>
+      </c>
+      <c r="D241" t="s">
+        <v>62</v>
+      </c>
+      <c r="E241" s="1" t="s">
+        <v>425</v>
+      </c>
+      <c r="G241" s="1"/>
+    </row>
+    <row r="242" spans="2:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="B242" s="1" t="s">
+        <v>430</v>
+      </c>
+      <c r="C242" s="1" t="s">
+        <v>242</v>
+      </c>
+      <c r="D242" t="s">
+        <v>62</v>
+      </c>
+      <c r="E242" s="1" t="s">
+        <v>425</v>
+      </c>
+      <c r="G242" s="1"/>
+    </row>
+    <row r="243" spans="2:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="B243" s="1" t="s">
+        <v>431</v>
+      </c>
+      <c r="C243" s="1" t="s">
+        <v>242</v>
+      </c>
+      <c r="D243" t="s">
+        <v>62</v>
+      </c>
+      <c r="E243" s="1" t="s">
+        <v>425</v>
+      </c>
+      <c r="G243" s="1"/>
+    </row>
+    <row r="244" spans="2:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="B244" s="1" t="s">
+        <v>432</v>
+      </c>
+      <c r="C244" s="1" t="s">
+        <v>242</v>
+      </c>
+      <c r="D244" t="s">
+        <v>62</v>
+      </c>
+      <c r="E244" s="1" t="s">
+        <v>425</v>
+      </c>
+      <c r="G244" s="1"/>
+    </row>
+    <row r="245" spans="2:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="B245" s="1" t="s">
+        <v>433</v>
+      </c>
+      <c r="C245" s="1" t="s">
+        <v>242</v>
+      </c>
+      <c r="D245" t="s">
+        <v>62</v>
+      </c>
+      <c r="E245" s="1" t="s">
+        <v>425</v>
+      </c>
+      <c r="G245" s="1"/>
+    </row>
+    <row r="246" spans="2:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="B246" s="1" t="s">
+        <v>434</v>
+      </c>
+      <c r="C246" s="1" t="s">
+        <v>242</v>
+      </c>
+      <c r="D246" t="s">
+        <v>62</v>
+      </c>
+      <c r="E246" s="1" t="s">
+        <v>425</v>
+      </c>
+      <c r="G246" s="1"/>
+    </row>
+    <row r="247" spans="2:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="B247" s="1" t="s">
+        <v>435</v>
+      </c>
+      <c r="C247" s="1" t="s">
+        <v>242</v>
+      </c>
+      <c r="D247" t="s">
+        <v>62</v>
+      </c>
+      <c r="E247" s="1" t="s">
+        <v>425</v>
+      </c>
+      <c r="G247" s="1"/>
+    </row>
+    <row r="248" spans="2:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="B248" s="1" t="s">
+        <v>436</v>
+      </c>
+      <c r="C248" s="1" t="s">
+        <v>242</v>
+      </c>
+      <c r="D248" t="s">
+        <v>62</v>
+      </c>
+      <c r="E248" s="1" t="s">
+        <v>425</v>
+      </c>
+      <c r="G248" s="1"/>
+    </row>
+    <row r="249" spans="2:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="B249" s="1" t="s">
+        <v>437</v>
+      </c>
+      <c r="C249" s="1" t="s">
+        <v>242</v>
+      </c>
+      <c r="D249" t="s">
+        <v>62</v>
+      </c>
+      <c r="E249" s="1" t="s">
+        <v>425</v>
+      </c>
+      <c r="G249" s="1"/>
+    </row>
+    <row r="250" spans="2:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="B250" s="1" t="s">
+        <v>438</v>
+      </c>
+      <c r="C250" s="1" t="s">
+        <v>242</v>
+      </c>
+      <c r="D250" t="s">
+        <v>62</v>
+      </c>
+      <c r="E250" s="1" t="s">
+        <v>425</v>
+      </c>
+      <c r="G250" s="1"/>
+    </row>
+    <row r="251" spans="2:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="B251" s="1" t="s">
         <v>439</v>
       </c>
-      <c r="C234" s="1" t="s">
+      <c r="C251" s="1" t="s">
         <v>440</v>
       </c>
-      <c r="D234" t="s">
-        <v>62</v>
-      </c>
-      <c r="E234" s="1" t="s">
+      <c r="D251" t="s">
+        <v>62</v>
+      </c>
+      <c r="E251" s="1" t="s">
         <v>441</v>
       </c>
-      <c r="G234" s="1"/>
+      <c r="G251" s="1"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1"/>
